--- a/Result/Agents.xlsx
+++ b/Result/Agents.xlsx
@@ -528,13 +528,13 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
         <v>9</v>
@@ -543,10 +543,10 @@
         <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -738,13 +738,13 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="n">
         <v>9</v>
@@ -753,10 +753,10 @@
         <v>9</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -808,13 +808,13 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="n">
         <v>9</v>
@@ -823,10 +823,10 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -878,13 +878,13 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="n">
         <v>9</v>
@@ -893,10 +893,10 @@
         <v>9</v>
       </c>
       <c r="H13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -983,13 +983,13 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="n">
         <v>9</v>
@@ -998,10 +998,10 @@
         <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1158,13 +1158,13 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" t="n">
         <v>9</v>
@@ -1173,10 +1173,10 @@
         <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1473,13 +1473,13 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F30" t="n">
         <v>9</v>
@@ -1488,10 +1488,10 @@
         <v>9</v>
       </c>
       <c r="H30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1578,13 +1578,13 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F33" t="n">
         <v>9</v>
@@ -1593,10 +1593,10 @@
         <v>9</v>
       </c>
       <c r="H33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1683,13 +1683,13 @@
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F36" t="n">
         <v>9</v>
@@ -1698,10 +1698,10 @@
         <v>9</v>
       </c>
       <c r="H36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1718,13 +1718,13 @@
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F37" t="n">
         <v>9</v>
@@ -1733,10 +1733,10 @@
         <v>9</v>
       </c>
       <c r="H37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -1893,13 +1893,13 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F42" t="n">
         <v>9</v>
@@ -1908,10 +1908,10 @@
         <v>9</v>
       </c>
       <c r="H42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -1963,13 +1963,13 @@
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F44" t="n">
         <v>9</v>
@@ -1978,10 +1978,10 @@
         <v>9</v>
       </c>
       <c r="H44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2068,13 +2068,13 @@
         <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F47" t="n">
         <v>9</v>
@@ -2083,10 +2083,10 @@
         <v>9</v>
       </c>
       <c r="H47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2173,13 +2173,13 @@
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F50" t="n">
         <v>9</v>
@@ -2188,10 +2188,10 @@
         <v>9</v>
       </c>
       <c r="H50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2278,13 +2278,13 @@
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F53" t="n">
         <v>9</v>
@@ -2293,10 +2293,10 @@
         <v>9</v>
       </c>
       <c r="H53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2453,13 +2453,13 @@
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F58" t="n">
         <v>9</v>
@@ -2468,10 +2468,10 @@
         <v>9</v>
       </c>
       <c r="H58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -2768,13 +2768,13 @@
         <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E67" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F67" t="n">
         <v>9</v>
@@ -2783,10 +2783,10 @@
         <v>9</v>
       </c>
       <c r="H67" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I67" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -2803,13 +2803,13 @@
         <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F68" t="n">
         <v>9</v>
@@ -2818,10 +2818,10 @@
         <v>9</v>
       </c>
       <c r="H68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I68" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -2838,13 +2838,13 @@
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F69" t="n">
         <v>9</v>
@@ -2853,10 +2853,10 @@
         <v>9</v>
       </c>
       <c r="H69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I69" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -2873,13 +2873,13 @@
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E70" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F70" t="n">
         <v>9</v>
@@ -2888,10 +2888,10 @@
         <v>9</v>
       </c>
       <c r="H70" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I70" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -2943,13 +2943,13 @@
         <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F72" t="n">
         <v>9</v>
@@ -2958,10 +2958,10 @@
         <v>9</v>
       </c>
       <c r="H72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I72" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3048,13 +3048,13 @@
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E75" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F75" t="n">
         <v>9</v>
@@ -3063,10 +3063,10 @@
         <v>9</v>
       </c>
       <c r="H75" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I75" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3083,13 +3083,13 @@
         <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E76" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F76" t="n">
         <v>9</v>
@@ -3098,10 +3098,10 @@
         <v>9</v>
       </c>
       <c r="H76" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I76" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3153,13 +3153,13 @@
         <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E78" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F78" t="n">
         <v>9</v>
@@ -3168,10 +3168,10 @@
         <v>9</v>
       </c>
       <c r="H78" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I78" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -3258,13 +3258,13 @@
         <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F81" t="n">
         <v>9</v>
@@ -3273,10 +3273,10 @@
         <v>9</v>
       </c>
       <c r="H81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I81" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -3363,13 +3363,13 @@
         <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E84" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F84" t="n">
         <v>9</v>
@@ -3378,10 +3378,10 @@
         <v>9</v>
       </c>
       <c r="H84" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I84" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -3538,13 +3538,13 @@
         <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E89" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F89" t="n">
         <v>9</v>
@@ -3553,10 +3553,10 @@
         <v>9</v>
       </c>
       <c r="H89" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I89" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -3678,13 +3678,13 @@
         <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E93" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
         <v>9</v>
@@ -3693,10 +3693,10 @@
         <v>9</v>
       </c>
       <c r="H93" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I93" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -3713,13 +3713,13 @@
         <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E94" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F94" t="n">
         <v>9</v>
@@ -3728,10 +3728,10 @@
         <v>9</v>
       </c>
       <c r="H94" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I94" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -3853,13 +3853,13 @@
         <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E98" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F98" t="n">
         <v>9</v>
@@ -3868,10 +3868,10 @@
         <v>9</v>
       </c>
       <c r="H98" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I98" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -3888,19 +3888,19 @@
         <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E99" t="n">
         <v>9</v>
       </c>
       <c r="F99" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G99" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H99" t="n">
         <v>9</v>
@@ -3958,19 +3958,19 @@
         <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E101" t="n">
         <v>9</v>
       </c>
       <c r="F101" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G101" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H101" t="n">
         <v>9</v>
@@ -4028,19 +4028,19 @@
         <v>1</v>
       </c>
       <c r="C103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E103" t="n">
         <v>9</v>
       </c>
       <c r="F103" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G103" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H103" t="n">
         <v>9</v>
@@ -4063,19 +4063,19 @@
         <v>1</v>
       </c>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E104" t="n">
         <v>9</v>
       </c>
       <c r="F104" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G104" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H104" t="n">
         <v>9</v>
@@ -4098,19 +4098,19 @@
         <v>1</v>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E105" t="n">
         <v>9</v>
       </c>
       <c r="F105" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G105" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H105" t="n">
         <v>9</v>
@@ -4168,19 +4168,19 @@
         <v>1</v>
       </c>
       <c r="C107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E107" t="n">
         <v>9</v>
       </c>
       <c r="F107" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G107" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H107" t="n">
         <v>9</v>
@@ -4203,19 +4203,19 @@
         <v>1</v>
       </c>
       <c r="C108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E108" t="n">
         <v>9</v>
       </c>
       <c r="F108" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G108" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H108" t="n">
         <v>9</v>
@@ -4238,19 +4238,19 @@
         <v>1</v>
       </c>
       <c r="C109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E109" t="n">
         <v>9</v>
       </c>
       <c r="F109" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G109" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H109" t="n">
         <v>9</v>
@@ -4273,19 +4273,19 @@
         <v>1</v>
       </c>
       <c r="C110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E110" t="n">
         <v>9</v>
       </c>
       <c r="F110" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G110" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H110" t="n">
         <v>9</v>
@@ -4308,19 +4308,19 @@
         <v>1</v>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E111" t="n">
         <v>9</v>
       </c>
       <c r="F111" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G111" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H111" t="n">
         <v>9</v>
@@ -4378,19 +4378,19 @@
         <v>1</v>
       </c>
       <c r="C113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E113" t="n">
         <v>9</v>
       </c>
       <c r="F113" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G113" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H113" t="n">
         <v>9</v>
@@ -4413,19 +4413,19 @@
         <v>1</v>
       </c>
       <c r="C114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E114" t="n">
         <v>9</v>
       </c>
       <c r="F114" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G114" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H114" t="n">
         <v>9</v>
@@ -4448,19 +4448,19 @@
         <v>1</v>
       </c>
       <c r="C115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E115" t="n">
         <v>9</v>
       </c>
       <c r="F115" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G115" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H115" t="n">
         <v>9</v>
@@ -4483,19 +4483,19 @@
         <v>1</v>
       </c>
       <c r="C116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E116" t="n">
         <v>9</v>
       </c>
       <c r="F116" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G116" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H116" t="n">
         <v>9</v>
@@ -4518,19 +4518,19 @@
         <v>1</v>
       </c>
       <c r="C117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E117" t="n">
         <v>9</v>
       </c>
       <c r="F117" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G117" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H117" t="n">
         <v>9</v>
@@ -4553,19 +4553,19 @@
         <v>1</v>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E118" t="n">
         <v>9</v>
       </c>
       <c r="F118" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G118" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H118" t="n">
         <v>9</v>
@@ -4588,19 +4588,19 @@
         <v>1</v>
       </c>
       <c r="C119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E119" t="n">
         <v>9</v>
       </c>
       <c r="F119" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G119" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H119" t="n">
         <v>9</v>
@@ -4623,19 +4623,19 @@
         <v>1</v>
       </c>
       <c r="C120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E120" t="n">
         <v>9</v>
       </c>
       <c r="F120" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G120" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H120" t="n">
         <v>9</v>
@@ -4658,19 +4658,19 @@
         <v>1</v>
       </c>
       <c r="C121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E121" t="n">
         <v>9</v>
       </c>
       <c r="F121" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G121" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H121" t="n">
         <v>9</v>
@@ -4693,19 +4693,19 @@
         <v>1</v>
       </c>
       <c r="C122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E122" t="n">
         <v>9</v>
       </c>
       <c r="F122" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G122" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H122" t="n">
         <v>9</v>
@@ -4728,19 +4728,19 @@
         <v>1</v>
       </c>
       <c r="C123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E123" t="n">
         <v>9</v>
       </c>
       <c r="F123" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G123" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H123" t="n">
         <v>9</v>
@@ -4798,19 +4798,19 @@
         <v>1</v>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E125" t="n">
         <v>9</v>
       </c>
       <c r="F125" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G125" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H125" t="n">
         <v>9</v>
@@ -4833,19 +4833,19 @@
         <v>1</v>
       </c>
       <c r="C126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E126" t="n">
         <v>9</v>
       </c>
       <c r="F126" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G126" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H126" t="n">
         <v>9</v>
@@ -4868,19 +4868,19 @@
         <v>1</v>
       </c>
       <c r="C127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E127" t="n">
         <v>9</v>
       </c>
       <c r="F127" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G127" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H127" t="n">
         <v>9</v>
@@ -4903,19 +4903,19 @@
         <v>1</v>
       </c>
       <c r="C128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E128" t="n">
         <v>9</v>
       </c>
       <c r="F128" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G128" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H128" t="n">
         <v>9</v>
@@ -4938,16 +4938,16 @@
         <v>1</v>
       </c>
       <c r="C129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E129" t="n">
         <v>9</v>
       </c>
       <c r="F129" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G129" t="n">
         <v>8</v>
@@ -4956,7 +4956,7 @@
         <v>9</v>
       </c>
       <c r="I129" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -4973,16 +4973,16 @@
         <v>1</v>
       </c>
       <c r="C130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E130" t="n">
         <v>9</v>
       </c>
       <c r="F130" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G130" t="n">
         <v>8</v>
@@ -4991,7 +4991,7 @@
         <v>9</v>
       </c>
       <c r="I130" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -5008,16 +5008,16 @@
         <v>1</v>
       </c>
       <c r="C131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E131" t="n">
         <v>9</v>
       </c>
       <c r="F131" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G131" t="n">
         <v>8</v>
@@ -5026,7 +5026,7 @@
         <v>9</v>
       </c>
       <c r="I131" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -5043,16 +5043,16 @@
         <v>1</v>
       </c>
       <c r="C132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E132" t="n">
         <v>9</v>
       </c>
       <c r="F132" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G132" t="n">
         <v>8</v>
@@ -5061,7 +5061,7 @@
         <v>9</v>
       </c>
       <c r="I132" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -5078,16 +5078,16 @@
         <v>1</v>
       </c>
       <c r="C133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E133" t="n">
         <v>9</v>
       </c>
       <c r="F133" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G133" t="n">
         <v>8</v>
@@ -5096,7 +5096,7 @@
         <v>9</v>
       </c>
       <c r="I133" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -5113,16 +5113,16 @@
         <v>1</v>
       </c>
       <c r="C134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D134" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E134" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F134" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G134" t="n">
         <v>8</v>
@@ -5148,16 +5148,16 @@
         <v>1</v>
       </c>
       <c r="C135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E135" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F135" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G135" t="n">
         <v>8</v>
@@ -5183,13 +5183,13 @@
         <v>1</v>
       </c>
       <c r="C136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D136" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E136" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F136" t="n">
         <v>8</v>
@@ -5988,13 +5988,13 @@
         <v>1</v>
       </c>
       <c r="C159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D159" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E159" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F159" t="n">
         <v>8</v>
@@ -6058,13 +6058,13 @@
         <v>1</v>
       </c>
       <c r="C161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D161" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E161" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F161" t="n">
         <v>8</v>
@@ -6093,13 +6093,13 @@
         <v>1</v>
       </c>
       <c r="C162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D162" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E162" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F162" t="n">
         <v>8</v>
@@ -6128,13 +6128,13 @@
         <v>1</v>
       </c>
       <c r="C163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D163" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E163" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F163" t="n">
         <v>8</v>
@@ -6163,13 +6163,13 @@
         <v>1</v>
       </c>
       <c r="C164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D164" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E164" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F164" t="n">
         <v>8</v>
@@ -6198,13 +6198,13 @@
         <v>1</v>
       </c>
       <c r="C165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D165" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E165" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F165" t="n">
         <v>8</v>
@@ -6239,7 +6239,7 @@
         <v>41</v>
       </c>
       <c r="E166" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F166" t="n">
         <v>8</v>
@@ -6251,7 +6251,7 @@
         <v>8</v>
       </c>
       <c r="I166" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -6274,7 +6274,7 @@
         <v>41</v>
       </c>
       <c r="E167" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F167" t="n">
         <v>8</v>
@@ -6286,7 +6286,7 @@
         <v>8</v>
       </c>
       <c r="I167" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
         <v>41</v>
       </c>
       <c r="E168" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F168" t="n">
         <v>8</v>
@@ -6321,7 +6321,7 @@
         <v>8</v>
       </c>
       <c r="I168" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -6344,7 +6344,7 @@
         <v>41</v>
       </c>
       <c r="E169" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F169" t="n">
         <v>8</v>
@@ -6356,7 +6356,7 @@
         <v>8</v>
       </c>
       <c r="I169" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
         <v>41</v>
       </c>
       <c r="E171" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F171" t="n">
         <v>8</v>
@@ -6426,7 +6426,7 @@
         <v>8</v>
       </c>
       <c r="I171" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -6484,7 +6484,7 @@
         <v>41</v>
       </c>
       <c r="E173" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F173" t="n">
         <v>8</v>
@@ -6496,7 +6496,7 @@
         <v>8</v>
       </c>
       <c r="I173" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -6519,7 +6519,7 @@
         <v>41</v>
       </c>
       <c r="E174" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F174" t="n">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>8</v>
       </c>
       <c r="I174" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -6554,7 +6554,7 @@
         <v>41</v>
       </c>
       <c r="E175" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F175" t="n">
         <v>8</v>
@@ -6566,7 +6566,7 @@
         <v>8</v>
       </c>
       <c r="I175" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -6589,7 +6589,7 @@
         <v>41</v>
       </c>
       <c r="E176" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F176" t="n">
         <v>8</v>
@@ -6601,7 +6601,7 @@
         <v>8</v>
       </c>
       <c r="I176" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -6624,7 +6624,7 @@
         <v>41</v>
       </c>
       <c r="E177" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F177" t="n">
         <v>8</v>
@@ -6636,7 +6636,7 @@
         <v>8</v>
       </c>
       <c r="I177" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -6659,7 +6659,7 @@
         <v>41</v>
       </c>
       <c r="E178" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F178" t="n">
         <v>8</v>
@@ -6671,7 +6671,7 @@
         <v>8</v>
       </c>
       <c r="I178" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -6694,7 +6694,7 @@
         <v>41</v>
       </c>
       <c r="E179" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F179" t="n">
         <v>8</v>
@@ -6706,7 +6706,7 @@
         <v>8</v>
       </c>
       <c r="I179" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -6729,7 +6729,7 @@
         <v>41</v>
       </c>
       <c r="E180" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F180" t="n">
         <v>8</v>
@@ -6741,7 +6741,7 @@
         <v>8</v>
       </c>
       <c r="I180" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -6764,7 +6764,7 @@
         <v>41</v>
       </c>
       <c r="E181" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F181" t="n">
         <v>8</v>
@@ -6776,7 +6776,7 @@
         <v>8</v>
       </c>
       <c r="I181" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -6799,7 +6799,7 @@
         <v>41</v>
       </c>
       <c r="E182" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F182" t="n">
         <v>8</v>
@@ -6811,7 +6811,7 @@
         <v>8</v>
       </c>
       <c r="I182" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -6834,7 +6834,7 @@
         <v>41</v>
       </c>
       <c r="E183" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F183" t="n">
         <v>8</v>
@@ -6846,7 +6846,7 @@
         <v>8</v>
       </c>
       <c r="I183" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -6904,7 +6904,7 @@
         <v>41</v>
       </c>
       <c r="E185" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F185" t="n">
         <v>8</v>
@@ -6916,7 +6916,7 @@
         <v>8</v>
       </c>
       <c r="I185" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -6939,7 +6939,7 @@
         <v>41</v>
       </c>
       <c r="E186" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F186" t="n">
         <v>8</v>
@@ -6951,7 +6951,7 @@
         <v>8</v>
       </c>
       <c r="I186" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -6968,25 +6968,25 @@
         <v>1</v>
       </c>
       <c r="C187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D187" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E187" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F187" t="n">
         <v>8</v>
       </c>
       <c r="G187" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H187" t="n">
         <v>8</v>
       </c>
       <c r="I187" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -7038,25 +7038,25 @@
         <v>1</v>
       </c>
       <c r="C189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D189" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E189" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F189" t="n">
         <v>8</v>
       </c>
       <c r="G189" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H189" t="n">
         <v>8</v>
       </c>
       <c r="I189" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -7073,25 +7073,25 @@
         <v>1</v>
       </c>
       <c r="C190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D190" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E190" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F190" t="n">
         <v>8</v>
       </c>
       <c r="G190" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H190" t="n">
         <v>8</v>
       </c>
       <c r="I190" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -7108,25 +7108,25 @@
         <v>1</v>
       </c>
       <c r="C191" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D191" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E191" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F191" t="n">
         <v>8</v>
       </c>
       <c r="G191" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H191" t="n">
         <v>8</v>
       </c>
       <c r="I191" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -7143,25 +7143,25 @@
         <v>1</v>
       </c>
       <c r="C192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D192" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E192" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F192" t="n">
         <v>8</v>
       </c>
       <c r="G192" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H192" t="n">
         <v>8</v>
       </c>
       <c r="I192" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -7178,25 +7178,25 @@
         <v>1</v>
       </c>
       <c r="C193" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D193" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E193" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F193" t="n">
         <v>8</v>
       </c>
       <c r="G193" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H193" t="n">
         <v>8</v>
       </c>
       <c r="I193" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -7225,13 +7225,13 @@
         <v>8</v>
       </c>
       <c r="G194" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H194" t="n">
         <v>8</v>
       </c>
       <c r="I194" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -7248,10 +7248,10 @@
         <v>1</v>
       </c>
       <c r="C195" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D195" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E195" t="n">
         <v>8</v>
@@ -7260,7 +7260,7 @@
         <v>8</v>
       </c>
       <c r="G195" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H195" t="n">
         <v>8</v>
@@ -7283,10 +7283,10 @@
         <v>1</v>
       </c>
       <c r="C196" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D196" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E196" t="n">
         <v>8</v>
@@ -7295,7 +7295,7 @@
         <v>8</v>
       </c>
       <c r="G196" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H196" t="n">
         <v>8</v>
@@ -7353,10 +7353,10 @@
         <v>1</v>
       </c>
       <c r="C198" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D198" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E198" t="n">
         <v>8</v>
@@ -7365,7 +7365,7 @@
         <v>8</v>
       </c>
       <c r="G198" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H198" t="n">
         <v>8</v>
@@ -7388,10 +7388,10 @@
         <v>1</v>
       </c>
       <c r="C199" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D199" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E199" t="n">
         <v>8</v>
@@ -7400,7 +7400,7 @@
         <v>8</v>
       </c>
       <c r="G199" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H199" t="n">
         <v>8</v>
@@ -7423,10 +7423,10 @@
         <v>1</v>
       </c>
       <c r="C200" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D200" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E200" t="n">
         <v>8</v>
@@ -7435,7 +7435,7 @@
         <v>8</v>
       </c>
       <c r="G200" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H200" t="n">
         <v>8</v>
@@ -7458,10 +7458,10 @@
         <v>1</v>
       </c>
       <c r="C201" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D201" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E201" t="n">
         <v>8</v>
@@ -7470,7 +7470,7 @@
         <v>8</v>
       </c>
       <c r="G201" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H201" t="n">
         <v>8</v>
@@ -7493,10 +7493,10 @@
         <v>1</v>
       </c>
       <c r="C202" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D202" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E202" t="n">
         <v>8</v>
@@ -7505,7 +7505,7 @@
         <v>8</v>
       </c>
       <c r="G202" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H202" t="n">
         <v>8</v>
@@ -7528,10 +7528,10 @@
         <v>1</v>
       </c>
       <c r="C203" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D203" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E203" t="n">
         <v>8</v>
@@ -7540,7 +7540,7 @@
         <v>8</v>
       </c>
       <c r="G203" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H203" t="n">
         <v>8</v>
@@ -7563,16 +7563,16 @@
         <v>1</v>
       </c>
       <c r="C204" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D204" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E204" t="n">
         <v>8</v>
       </c>
       <c r="F204" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G204" t="n">
         <v>8</v>
@@ -7633,16 +7633,16 @@
         <v>1</v>
       </c>
       <c r="C206" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D206" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E206" t="n">
         <v>8</v>
       </c>
       <c r="F206" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G206" t="n">
         <v>8</v>
@@ -7668,22 +7668,22 @@
         <v>1</v>
       </c>
       <c r="C207" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D207" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E207" t="n">
         <v>8</v>
       </c>
       <c r="F207" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G207" t="n">
         <v>8</v>
       </c>
       <c r="H207" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I207" t="n">
         <v>8</v>
@@ -7738,22 +7738,22 @@
         <v>1</v>
       </c>
       <c r="C209" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D209" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E209" t="n">
         <v>8</v>
       </c>
       <c r="F209" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G209" t="n">
         <v>8</v>
       </c>
       <c r="H209" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I209" t="n">
         <v>8</v>
@@ -7773,22 +7773,22 @@
         <v>1</v>
       </c>
       <c r="C210" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D210" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E210" t="n">
         <v>8</v>
       </c>
       <c r="F210" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G210" t="n">
         <v>8</v>
       </c>
       <c r="H210" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I210" t="n">
         <v>8</v>
@@ -7808,22 +7808,22 @@
         <v>1</v>
       </c>
       <c r="C211" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D211" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E211" t="n">
         <v>8</v>
       </c>
       <c r="F211" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G211" t="n">
         <v>8</v>
       </c>
       <c r="H211" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I211" t="n">
         <v>8</v>
@@ -7843,22 +7843,22 @@
         <v>1</v>
       </c>
       <c r="C212" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D212" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E212" t="n">
         <v>8</v>
       </c>
       <c r="F212" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G212" t="n">
         <v>8</v>
       </c>
       <c r="H212" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I212" t="n">
         <v>8</v>
@@ -7878,22 +7878,22 @@
         <v>1</v>
       </c>
       <c r="C213" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D213" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E213" t="n">
         <v>8</v>
       </c>
       <c r="F213" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G213" t="n">
         <v>8</v>
       </c>
       <c r="H213" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I213" t="n">
         <v>8</v>
@@ -7913,22 +7913,22 @@
         <v>1</v>
       </c>
       <c r="C214" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D214" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E214" t="n">
         <v>8</v>
       </c>
       <c r="F214" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G214" t="n">
         <v>8</v>
       </c>
       <c r="H214" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I214" t="n">
         <v>8</v>
@@ -7948,22 +7948,22 @@
         <v>1</v>
       </c>
       <c r="C215" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D215" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E215" t="n">
         <v>8</v>
       </c>
       <c r="F215" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G215" t="n">
         <v>8</v>
       </c>
       <c r="H215" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I215" t="n">
         <v>8</v>
@@ -7983,22 +7983,22 @@
         <v>1</v>
       </c>
       <c r="C216" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D216" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E216" t="n">
         <v>8</v>
       </c>
       <c r="F216" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G216" t="n">
         <v>8</v>
       </c>
       <c r="H216" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I216" t="n">
         <v>8</v>
@@ -8018,22 +8018,22 @@
         <v>1</v>
       </c>
       <c r="C217" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D217" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E217" t="n">
         <v>8</v>
       </c>
       <c r="F217" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G217" t="n">
         <v>8</v>
       </c>
       <c r="H217" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I217" t="n">
         <v>8</v>
@@ -8053,22 +8053,22 @@
         <v>1</v>
       </c>
       <c r="C218" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D218" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E218" t="n">
         <v>8</v>
       </c>
       <c r="F218" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G218" t="n">
         <v>8</v>
       </c>
       <c r="H218" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I218" t="n">
         <v>8</v>
@@ -8088,22 +8088,22 @@
         <v>1</v>
       </c>
       <c r="C219" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D219" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E219" t="n">
         <v>8</v>
       </c>
       <c r="F219" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G219" t="n">
         <v>8</v>
       </c>
       <c r="H219" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I219" t="n">
         <v>8</v>
@@ -8123,22 +8123,22 @@
         <v>1</v>
       </c>
       <c r="C220" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D220" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E220" t="n">
         <v>8</v>
       </c>
       <c r="F220" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G220" t="n">
         <v>8</v>
       </c>
       <c r="H220" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I220" t="n">
         <v>8</v>
@@ -8158,10 +8158,10 @@
         <v>1</v>
       </c>
       <c r="C221" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D221" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E221" t="n">
         <v>8</v>
@@ -8173,7 +8173,7 @@
         <v>8</v>
       </c>
       <c r="H221" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I221" t="n">
         <v>8</v>
@@ -8193,10 +8193,10 @@
         <v>1</v>
       </c>
       <c r="C222" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D222" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E222" t="n">
         <v>8</v>
@@ -8208,7 +8208,7 @@
         <v>8</v>
       </c>
       <c r="H222" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I222" t="n">
         <v>8</v>
@@ -8228,10 +8228,10 @@
         <v>1</v>
       </c>
       <c r="C223" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D223" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E223" t="n">
         <v>8</v>
@@ -8240,7 +8240,7 @@
         <v>8</v>
       </c>
       <c r="G223" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H223" t="n">
         <v>8</v>
@@ -8263,10 +8263,10 @@
         <v>1</v>
       </c>
       <c r="C224" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D224" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E224" t="n">
         <v>8</v>
@@ -8275,7 +8275,7 @@
         <v>8</v>
       </c>
       <c r="G224" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H224" t="n">
         <v>8</v>
@@ -8298,10 +8298,10 @@
         <v>1</v>
       </c>
       <c r="C225" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D225" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E225" t="n">
         <v>8</v>
@@ -8310,7 +8310,7 @@
         <v>8</v>
       </c>
       <c r="G225" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H225" t="n">
         <v>8</v>
@@ -8333,10 +8333,10 @@
         <v>1</v>
       </c>
       <c r="C226" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D226" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E226" t="n">
         <v>8</v>
@@ -8345,7 +8345,7 @@
         <v>8</v>
       </c>
       <c r="G226" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H226" t="n">
         <v>8</v>
@@ -8368,10 +8368,10 @@
         <v>1</v>
       </c>
       <c r="C227" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D227" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E227" t="n">
         <v>8</v>
@@ -8380,7 +8380,7 @@
         <v>8</v>
       </c>
       <c r="G227" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H227" t="n">
         <v>8</v>
@@ -8403,10 +8403,10 @@
         <v>1</v>
       </c>
       <c r="C228" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D228" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E228" t="n">
         <v>8</v>
@@ -8415,7 +8415,7 @@
         <v>8</v>
       </c>
       <c r="G228" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H228" t="n">
         <v>8</v>
@@ -8438,10 +8438,10 @@
         <v>1</v>
       </c>
       <c r="C229" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D229" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E229" t="n">
         <v>8</v>
@@ -8450,7 +8450,7 @@
         <v>8</v>
       </c>
       <c r="G229" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H229" t="n">
         <v>8</v>
@@ -8473,10 +8473,10 @@
         <v>1</v>
       </c>
       <c r="C230" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D230" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E230" t="n">
         <v>8</v>
@@ -8485,7 +8485,7 @@
         <v>8</v>
       </c>
       <c r="G230" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H230" t="n">
         <v>8</v>
@@ -8508,10 +8508,10 @@
         <v>1</v>
       </c>
       <c r="C231" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D231" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E231" t="n">
         <v>8</v>
@@ -8520,7 +8520,7 @@
         <v>8</v>
       </c>
       <c r="G231" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H231" t="n">
         <v>8</v>
@@ -8543,10 +8543,10 @@
         <v>1</v>
       </c>
       <c r="C232" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D232" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E232" t="n">
         <v>8</v>
@@ -8555,7 +8555,7 @@
         <v>8</v>
       </c>
       <c r="G232" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H232" t="n">
         <v>8</v>
@@ -8578,10 +8578,10 @@
         <v>1</v>
       </c>
       <c r="C233" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D233" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E233" t="n">
         <v>8</v>
@@ -8590,7 +8590,7 @@
         <v>8</v>
       </c>
       <c r="G233" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H233" t="n">
         <v>8</v>
@@ -8613,10 +8613,10 @@
         <v>1</v>
       </c>
       <c r="C234" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D234" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E234" t="n">
         <v>8</v>
@@ -8625,7 +8625,7 @@
         <v>8</v>
       </c>
       <c r="G234" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H234" t="n">
         <v>8</v>
@@ -8648,10 +8648,10 @@
         <v>1</v>
       </c>
       <c r="C235" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D235" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E235" t="n">
         <v>8</v>
@@ -8660,7 +8660,7 @@
         <v>8</v>
       </c>
       <c r="G235" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H235" t="n">
         <v>8</v>
@@ -8683,16 +8683,16 @@
         <v>1</v>
       </c>
       <c r="C236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D236" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E236" t="n">
         <v>8</v>
       </c>
       <c r="F236" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G236" t="n">
         <v>9</v>
@@ -8718,16 +8718,16 @@
         <v>1</v>
       </c>
       <c r="C237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D237" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E237" t="n">
         <v>8</v>
       </c>
       <c r="F237" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G237" t="n">
         <v>9</v>
@@ -8753,22 +8753,22 @@
         <v>1</v>
       </c>
       <c r="C238" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D238" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E238" t="n">
         <v>8</v>
       </c>
       <c r="F238" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G238" t="n">
         <v>9</v>
       </c>
       <c r="H238" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I238" t="n">
         <v>8</v>
@@ -8788,22 +8788,22 @@
         <v>1</v>
       </c>
       <c r="C239" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D239" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E239" t="n">
         <v>8</v>
       </c>
       <c r="F239" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G239" t="n">
         <v>9</v>
       </c>
       <c r="H239" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I239" t="n">
         <v>8</v>
@@ -8823,22 +8823,22 @@
         <v>1</v>
       </c>
       <c r="C240" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D240" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E240" t="n">
         <v>8</v>
       </c>
       <c r="F240" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G240" t="n">
         <v>9</v>
       </c>
       <c r="H240" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I240" t="n">
         <v>8</v>
@@ -8858,22 +8858,22 @@
         <v>1</v>
       </c>
       <c r="C241" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D241" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E241" t="n">
         <v>8</v>
       </c>
       <c r="F241" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G241" t="n">
         <v>9</v>
       </c>
       <c r="H241" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I241" t="n">
         <v>8</v>
@@ -8893,22 +8893,22 @@
         <v>1</v>
       </c>
       <c r="C242" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D242" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E242" t="n">
         <v>8</v>
       </c>
       <c r="F242" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G242" t="n">
         <v>9</v>
       </c>
       <c r="H242" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I242" t="n">
         <v>8</v>
@@ -8928,22 +8928,22 @@
         <v>1</v>
       </c>
       <c r="C243" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D243" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E243" t="n">
         <v>8</v>
       </c>
       <c r="F243" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G243" t="n">
         <v>9</v>
       </c>
       <c r="H243" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I243" t="n">
         <v>8</v>
@@ -8963,22 +8963,22 @@
         <v>1</v>
       </c>
       <c r="C244" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D244" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E244" t="n">
         <v>8</v>
       </c>
       <c r="F244" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G244" t="n">
         <v>9</v>
       </c>
       <c r="H244" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I244" t="n">
         <v>8</v>
@@ -8998,22 +8998,22 @@
         <v>1</v>
       </c>
       <c r="C245" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D245" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E245" t="n">
         <v>8</v>
       </c>
       <c r="F245" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G245" t="n">
         <v>9</v>
       </c>
       <c r="H245" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I245" t="n">
         <v>8</v>
@@ -9033,22 +9033,22 @@
         <v>1</v>
       </c>
       <c r="C246" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D246" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E246" t="n">
         <v>8</v>
       </c>
       <c r="F246" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G246" t="n">
         <v>9</v>
       </c>
       <c r="H246" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I246" t="n">
         <v>8</v>
@@ -9068,16 +9068,16 @@
         <v>1</v>
       </c>
       <c r="C247" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D247" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E247" t="n">
         <v>8</v>
       </c>
       <c r="F247" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G247" t="n">
         <v>9</v>
@@ -9103,16 +9103,16 @@
         <v>1</v>
       </c>
       <c r="C248" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D248" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E248" t="n">
         <v>8</v>
       </c>
       <c r="F248" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G248" t="n">
         <v>9</v>
@@ -9138,16 +9138,16 @@
         <v>1</v>
       </c>
       <c r="C249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D249" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E249" t="n">
         <v>8</v>
       </c>
       <c r="F249" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G249" t="n">
         <v>9</v>
@@ -9173,16 +9173,16 @@
         <v>1</v>
       </c>
       <c r="C250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D250" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E250" t="n">
         <v>8</v>
       </c>
       <c r="F250" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G250" t="n">
         <v>9</v>
@@ -9208,16 +9208,16 @@
         <v>1</v>
       </c>
       <c r="C251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D251" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E251" t="n">
         <v>8</v>
       </c>
       <c r="F251" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G251" t="n">
         <v>9</v>
@@ -9243,16 +9243,16 @@
         <v>1</v>
       </c>
       <c r="C252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D252" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E252" t="n">
         <v>8</v>
       </c>
       <c r="F252" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G252" t="n">
         <v>9</v>
@@ -9278,16 +9278,16 @@
         <v>1</v>
       </c>
       <c r="C253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D253" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E253" t="n">
         <v>8</v>
       </c>
       <c r="F253" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G253" t="n">
         <v>9</v>
@@ -9313,16 +9313,16 @@
         <v>1</v>
       </c>
       <c r="C254" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D254" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E254" t="n">
         <v>8</v>
       </c>
       <c r="F254" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G254" t="n">
         <v>9</v>
@@ -9348,16 +9348,16 @@
         <v>1</v>
       </c>
       <c r="C255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D255" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E255" t="n">
         <v>8</v>
       </c>
       <c r="F255" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G255" t="n">
         <v>9</v>
@@ -9383,16 +9383,16 @@
         <v>1</v>
       </c>
       <c r="C256" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D256" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E256" t="n">
         <v>8</v>
       </c>
       <c r="F256" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G256" t="n">
         <v>9</v>
@@ -9427,10 +9427,10 @@
         <v>8</v>
       </c>
       <c r="F257" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G257" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H257" t="n">
         <v>9</v>
@@ -9453,10 +9453,10 @@
         <v>1</v>
       </c>
       <c r="C258" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D258" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E258" t="n">
         <v>8</v>
@@ -9465,7 +9465,7 @@
         <v>9</v>
       </c>
       <c r="G258" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H258" t="n">
         <v>9</v>
@@ -9488,10 +9488,10 @@
         <v>1</v>
       </c>
       <c r="C259" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D259" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E259" t="n">
         <v>8</v>
@@ -9500,7 +9500,7 @@
         <v>9</v>
       </c>
       <c r="G259" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H259" t="n">
         <v>9</v>
@@ -9523,10 +9523,10 @@
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D260" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E260" t="n">
         <v>8</v>
@@ -9535,7 +9535,7 @@
         <v>9</v>
       </c>
       <c r="G260" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H260" t="n">
         <v>9</v>
@@ -9558,10 +9558,10 @@
         <v>1</v>
       </c>
       <c r="C261" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D261" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E261" t="n">
         <v>8</v>
@@ -9570,7 +9570,7 @@
         <v>9</v>
       </c>
       <c r="G261" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H261" t="n">
         <v>9</v>
@@ -9628,10 +9628,10 @@
         <v>1</v>
       </c>
       <c r="C263" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D263" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E263" t="n">
         <v>8</v>
@@ -9640,7 +9640,7 @@
         <v>9</v>
       </c>
       <c r="G263" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H263" t="n">
         <v>9</v>
@@ -9663,10 +9663,10 @@
         <v>1</v>
       </c>
       <c r="C264" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D264" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E264" t="n">
         <v>8</v>
@@ -9675,13 +9675,13 @@
         <v>9</v>
       </c>
       <c r="G264" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H264" t="n">
         <v>9</v>
       </c>
       <c r="I264" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>1</v>
       </c>
       <c r="C265" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D265" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E265" t="n">
         <v>8</v>
@@ -9710,13 +9710,13 @@
         <v>9</v>
       </c>
       <c r="G265" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H265" t="n">
         <v>9</v>
       </c>
       <c r="I265" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -9733,10 +9733,10 @@
         <v>1</v>
       </c>
       <c r="C266" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D266" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E266" t="n">
         <v>8</v>
@@ -9745,13 +9745,13 @@
         <v>9</v>
       </c>
       <c r="G266" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H266" t="n">
         <v>9</v>
       </c>
       <c r="I266" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -9803,25 +9803,25 @@
         <v>1</v>
       </c>
       <c r="C268" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D268" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E268" t="n">
         <v>8</v>
       </c>
       <c r="F268" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G268" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H268" t="n">
         <v>9</v>
       </c>
       <c r="I268" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -9838,25 +9838,25 @@
         <v>1</v>
       </c>
       <c r="C269" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D269" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E269" t="n">
         <v>8</v>
       </c>
       <c r="F269" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G269" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H269" t="n">
         <v>9</v>
       </c>
       <c r="I269" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -9873,25 +9873,25 @@
         <v>1</v>
       </c>
       <c r="C270" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D270" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E270" t="n">
         <v>8</v>
       </c>
       <c r="F270" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G270" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H270" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I270" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -9908,25 +9908,25 @@
         <v>1</v>
       </c>
       <c r="C271" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D271" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E271" t="n">
         <v>8</v>
       </c>
       <c r="F271" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G271" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H271" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I271" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -9943,25 +9943,25 @@
         <v>1</v>
       </c>
       <c r="C272" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D272" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E272" t="n">
         <v>8</v>
       </c>
       <c r="F272" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G272" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H272" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I272" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -9978,25 +9978,25 @@
         <v>1</v>
       </c>
       <c r="C273" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D273" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E273" t="n">
         <v>8</v>
       </c>
       <c r="F273" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G273" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H273" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I273" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -10013,25 +10013,25 @@
         <v>1</v>
       </c>
       <c r="C274" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D274" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E274" t="n">
         <v>8</v>
       </c>
       <c r="F274" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G274" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H274" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I274" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -10048,25 +10048,25 @@
         <v>1</v>
       </c>
       <c r="C275" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D275" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E275" t="n">
         <v>8</v>
       </c>
       <c r="F275" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G275" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H275" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I275" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -10083,25 +10083,25 @@
         <v>1</v>
       </c>
       <c r="C276" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D276" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E276" t="n">
         <v>8</v>
       </c>
       <c r="F276" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G276" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H276" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I276" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -10118,25 +10118,25 @@
         <v>1</v>
       </c>
       <c r="C277" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D277" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E277" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F277" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G277" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H277" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I277" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -10153,25 +10153,25 @@
         <v>1</v>
       </c>
       <c r="C278" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D278" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E278" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F278" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G278" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H278" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I278" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -10188,25 +10188,25 @@
         <v>1</v>
       </c>
       <c r="C279" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D279" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E279" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F279" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G279" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H279" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I279" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J279" t="n">
         <v>0</v>
@@ -10293,25 +10293,25 @@
         <v>1</v>
       </c>
       <c r="C282" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D282" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E282" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F282" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G282" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H282" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I282" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J282" t="n">
         <v>0</v>
@@ -10328,25 +10328,25 @@
         <v>1</v>
       </c>
       <c r="C283" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D283" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E283" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F283" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G283" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H283" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I283" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J283" t="n">
         <v>0</v>
@@ -10363,25 +10363,25 @@
         <v>1</v>
       </c>
       <c r="C284" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D284" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E284" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F284" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G284" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H284" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I284" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J284" t="n">
         <v>0</v>
@@ -10398,25 +10398,25 @@
         <v>1</v>
       </c>
       <c r="C285" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D285" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E285" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F285" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G285" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H285" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I285" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J285" t="n">
         <v>0</v>
@@ -10433,25 +10433,25 @@
         <v>1</v>
       </c>
       <c r="C286" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D286" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E286" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F286" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G286" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H286" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I286" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J286" t="n">
         <v>0</v>
@@ -10468,25 +10468,25 @@
         <v>1</v>
       </c>
       <c r="C287" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D287" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E287" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F287" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G287" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H287" t="n">
         <v>9</v>
       </c>
       <c r="I287" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J287" t="n">
         <v>0</v>
@@ -10503,25 +10503,25 @@
         <v>1</v>
       </c>
       <c r="C288" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D288" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E288" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F288" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G288" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H288" t="n">
         <v>9</v>
       </c>
       <c r="I288" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J288" t="n">
         <v>0</v>
@@ -10538,19 +10538,19 @@
         <v>1</v>
       </c>
       <c r="C289" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D289" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E289" t="n">
         <v>9</v>
       </c>
       <c r="F289" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G289" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H289" t="n">
         <v>9</v>
@@ -10573,19 +10573,19 @@
         <v>1</v>
       </c>
       <c r="C290" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D290" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E290" t="n">
         <v>9</v>
       </c>
       <c r="F290" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G290" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H290" t="n">
         <v>9</v>
@@ -10608,19 +10608,19 @@
         <v>1</v>
       </c>
       <c r="C291" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D291" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E291" t="n">
         <v>9</v>
       </c>
       <c r="F291" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G291" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H291" t="n">
         <v>9</v>
@@ -10643,19 +10643,19 @@
         <v>1</v>
       </c>
       <c r="C292" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D292" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E292" t="n">
         <v>9</v>
       </c>
       <c r="F292" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G292" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H292" t="n">
         <v>9</v>
@@ -10678,19 +10678,19 @@
         <v>1</v>
       </c>
       <c r="C293" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D293" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E293" t="n">
         <v>9</v>
       </c>
       <c r="F293" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G293" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H293" t="n">
         <v>9</v>
@@ -10713,19 +10713,19 @@
         <v>1</v>
       </c>
       <c r="C294" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D294" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E294" t="n">
         <v>9</v>
       </c>
       <c r="F294" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G294" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H294" t="n">
         <v>9</v>
@@ -10748,19 +10748,19 @@
         <v>1</v>
       </c>
       <c r="C295" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D295" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E295" t="n">
         <v>9</v>
       </c>
       <c r="F295" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G295" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H295" t="n">
         <v>9</v>
@@ -10783,19 +10783,19 @@
         <v>1</v>
       </c>
       <c r="C296" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D296" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E296" t="n">
         <v>9</v>
       </c>
       <c r="F296" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G296" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H296" t="n">
         <v>9</v>
@@ -10818,22 +10818,22 @@
         <v>1</v>
       </c>
       <c r="C297" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D297" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E297" t="n">
         <v>9</v>
       </c>
       <c r="F297" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G297" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H297" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I297" t="n">
         <v>8</v>
@@ -10853,22 +10853,22 @@
         <v>1</v>
       </c>
       <c r="C298" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D298" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E298" t="n">
         <v>9</v>
       </c>
       <c r="F298" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G298" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H298" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I298" t="n">
         <v>8</v>
@@ -10888,22 +10888,22 @@
         <v>1</v>
       </c>
       <c r="C299" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D299" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E299" t="n">
         <v>9</v>
       </c>
       <c r="F299" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G299" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H299" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I299" t="n">
         <v>8</v>
@@ -10923,22 +10923,22 @@
         <v>1</v>
       </c>
       <c r="C300" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D300" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E300" t="n">
         <v>9</v>
       </c>
       <c r="F300" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G300" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H300" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I300" t="n">
         <v>8</v>
@@ -10993,22 +10993,22 @@
         <v>1</v>
       </c>
       <c r="C302" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D302" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E302" t="n">
         <v>9</v>
       </c>
       <c r="F302" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G302" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H302" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I302" t="n">
         <v>8</v>
@@ -11063,22 +11063,22 @@
         <v>1</v>
       </c>
       <c r="C304" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D304" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E304" t="n">
         <v>9</v>
       </c>
       <c r="F304" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G304" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H304" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I304" t="n">
         <v>8</v>
@@ -11098,22 +11098,22 @@
         <v>1</v>
       </c>
       <c r="C305" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D305" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E305" t="n">
         <v>9</v>
       </c>
       <c r="F305" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G305" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H305" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I305" t="n">
         <v>8</v>
@@ -11133,22 +11133,22 @@
         <v>1</v>
       </c>
       <c r="C306" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D306" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E306" t="n">
         <v>9</v>
       </c>
       <c r="F306" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G306" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H306" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I306" t="n">
         <v>8</v>
@@ -11168,22 +11168,22 @@
         <v>1</v>
       </c>
       <c r="C307" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D307" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E307" t="n">
         <v>9</v>
       </c>
       <c r="F307" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G307" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H307" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I307" t="n">
         <v>8</v>
@@ -11203,22 +11203,22 @@
         <v>1</v>
       </c>
       <c r="C308" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D308" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E308" t="n">
         <v>9</v>
       </c>
       <c r="F308" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G308" t="n">
         <v>9</v>
       </c>
       <c r="H308" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I308" t="n">
         <v>8</v>
@@ -11238,22 +11238,22 @@
         <v>1</v>
       </c>
       <c r="C309" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D309" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E309" t="n">
         <v>9</v>
       </c>
       <c r="F309" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G309" t="n">
         <v>9</v>
       </c>
       <c r="H309" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I309" t="n">
         <v>8</v>
@@ -11273,22 +11273,22 @@
         <v>1</v>
       </c>
       <c r="C310" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D310" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E310" t="n">
         <v>9</v>
       </c>
       <c r="F310" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G310" t="n">
         <v>9</v>
       </c>
       <c r="H310" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I310" t="n">
         <v>8</v>
@@ -11308,22 +11308,22 @@
         <v>1</v>
       </c>
       <c r="C311" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D311" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E311" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F311" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G311" t="n">
         <v>9</v>
       </c>
       <c r="H311" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I311" t="n">
         <v>8</v>
@@ -11343,22 +11343,22 @@
         <v>1</v>
       </c>
       <c r="C312" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D312" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E312" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F312" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G312" t="n">
         <v>9</v>
       </c>
       <c r="H312" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I312" t="n">
         <v>8</v>
@@ -11378,16 +11378,16 @@
         <v>1</v>
       </c>
       <c r="C313" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D313" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E313" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F313" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G313" t="n">
         <v>9</v>
@@ -11396,7 +11396,7 @@
         <v>8</v>
       </c>
       <c r="I313" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J313" t="n">
         <v>0</v>
@@ -11413,16 +11413,16 @@
         <v>1</v>
       </c>
       <c r="C314" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D314" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E314" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F314" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G314" t="n">
         <v>9</v>
@@ -11431,7 +11431,7 @@
         <v>8</v>
       </c>
       <c r="I314" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J314" t="n">
         <v>0</v>
@@ -11518,16 +11518,16 @@
         <v>1</v>
       </c>
       <c r="C317" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D317" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E317" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F317" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G317" t="n">
         <v>9</v>
@@ -11536,7 +11536,7 @@
         <v>8</v>
       </c>
       <c r="I317" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J317" t="n">
         <v>0</v>
@@ -11553,25 +11553,25 @@
         <v>1</v>
       </c>
       <c r="C318" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D318" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E318" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F318" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G318" t="n">
         <v>9</v>
       </c>
       <c r="H318" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I318" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J318" t="n">
         <v>0</v>
@@ -11588,25 +11588,25 @@
         <v>1</v>
       </c>
       <c r="C319" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D319" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E319" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F319" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G319" t="n">
         <v>9</v>
       </c>
       <c r="H319" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I319" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J319" t="n">
         <v>0</v>
@@ -11623,25 +11623,25 @@
         <v>1</v>
       </c>
       <c r="C320" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D320" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E320" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F320" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G320" t="n">
         <v>9</v>
       </c>
       <c r="H320" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I320" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J320" t="n">
         <v>0</v>
@@ -11658,25 +11658,25 @@
         <v>1</v>
       </c>
       <c r="C321" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D321" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E321" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F321" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G321" t="n">
         <v>9</v>
       </c>
       <c r="H321" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I321" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J321" t="n">
         <v>0</v>
@@ -11693,25 +11693,25 @@
         <v>1</v>
       </c>
       <c r="C322" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D322" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E322" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F322" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G322" t="n">
         <v>9</v>
       </c>
       <c r="H322" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I322" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J322" t="n">
         <v>0</v>
@@ -11728,25 +11728,25 @@
         <v>1</v>
       </c>
       <c r="C323" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D323" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E323" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F323" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G323" t="n">
         <v>9</v>
       </c>
       <c r="H323" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I323" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J323" t="n">
         <v>0</v>
@@ -11763,25 +11763,25 @@
         <v>1</v>
       </c>
       <c r="C324" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D324" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E324" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F324" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G324" t="n">
         <v>9</v>
       </c>
       <c r="H324" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I324" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J324" t="n">
         <v>0</v>
@@ -11798,25 +11798,25 @@
         <v>1</v>
       </c>
       <c r="C325" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D325" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E325" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F325" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G325" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H325" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I325" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J325" t="n">
         <v>0</v>
@@ -11833,25 +11833,25 @@
         <v>1</v>
       </c>
       <c r="C326" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D326" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E326" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F326" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G326" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H326" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I326" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J326" t="n">
         <v>0</v>
@@ -11868,25 +11868,25 @@
         <v>1</v>
       </c>
       <c r="C327" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D327" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E327" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F327" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G327" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H327" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I327" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J327" t="n">
         <v>0</v>
@@ -11903,25 +11903,25 @@
         <v>1</v>
       </c>
       <c r="C328" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D328" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E328" t="n">
         <v>9</v>
       </c>
       <c r="F328" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G328" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H328" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I328" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J328" t="n">
         <v>0</v>
@@ -11938,25 +11938,25 @@
         <v>1</v>
       </c>
       <c r="C329" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D329" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E329" t="n">
         <v>9</v>
       </c>
       <c r="F329" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G329" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H329" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I329" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J329" t="n">
         <v>0</v>
@@ -11973,25 +11973,25 @@
         <v>1</v>
       </c>
       <c r="C330" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D330" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E330" t="n">
         <v>9</v>
       </c>
       <c r="F330" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G330" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H330" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I330" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J330" t="n">
         <v>0</v>
@@ -12008,25 +12008,25 @@
         <v>1</v>
       </c>
       <c r="C331" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D331" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E331" t="n">
         <v>9</v>
       </c>
       <c r="F331" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G331" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H331" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I331" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J331" t="n">
         <v>0</v>
@@ -12043,25 +12043,25 @@
         <v>1</v>
       </c>
       <c r="C332" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D332" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E332" t="n">
         <v>9</v>
       </c>
       <c r="F332" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G332" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H332" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I332" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J332" t="n">
         <v>0</v>
@@ -12078,25 +12078,25 @@
         <v>1</v>
       </c>
       <c r="C333" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D333" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E333" t="n">
         <v>9</v>
       </c>
       <c r="F333" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G333" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H333" t="n">
         <v>8</v>
       </c>
       <c r="I333" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J333" t="n">
         <v>0</v>
@@ -12113,25 +12113,25 @@
         <v>1</v>
       </c>
       <c r="C334" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D334" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E334" t="n">
         <v>9</v>
       </c>
       <c r="F334" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G334" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H334" t="n">
         <v>8</v>
       </c>
       <c r="I334" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J334" t="n">
         <v>0</v>
@@ -12148,25 +12148,25 @@
         <v>1</v>
       </c>
       <c r="C335" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D335" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E335" t="n">
         <v>9</v>
       </c>
       <c r="F335" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G335" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H335" t="n">
         <v>8</v>
       </c>
       <c r="I335" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J335" t="n">
         <v>0</v>
@@ -12183,25 +12183,25 @@
         <v>1</v>
       </c>
       <c r="C336" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D336" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E336" t="n">
         <v>9</v>
       </c>
       <c r="F336" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G336" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H336" t="n">
         <v>8</v>
       </c>
       <c r="I336" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J336" t="n">
         <v>0</v>
@@ -12218,25 +12218,25 @@
         <v>1</v>
       </c>
       <c r="C337" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D337" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E337" t="n">
         <v>9</v>
       </c>
       <c r="F337" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G337" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H337" t="n">
         <v>8</v>
       </c>
       <c r="I337" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J337" t="n">
         <v>0</v>
@@ -12253,25 +12253,25 @@
         <v>1</v>
       </c>
       <c r="C338" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D338" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E338" t="n">
         <v>9</v>
       </c>
       <c r="F338" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G338" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H338" t="n">
         <v>8</v>
       </c>
       <c r="I338" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J338" t="n">
         <v>0</v>
@@ -12288,25 +12288,25 @@
         <v>1</v>
       </c>
       <c r="C339" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D339" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E339" t="n">
         <v>9</v>
       </c>
       <c r="F339" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G339" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H339" t="n">
         <v>8</v>
       </c>
       <c r="I339" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J339" t="n">
         <v>0</v>
@@ -12323,16 +12323,16 @@
         <v>1</v>
       </c>
       <c r="C340" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D340" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E340" t="n">
         <v>9</v>
       </c>
       <c r="F340" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G340" t="n">
         <v>9</v>
@@ -12341,7 +12341,7 @@
         <v>8</v>
       </c>
       <c r="I340" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J340" t="n">
         <v>0</v>
@@ -12358,16 +12358,16 @@
         <v>1</v>
       </c>
       <c r="C341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D341" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E341" t="n">
         <v>9</v>
       </c>
       <c r="F341" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G341" t="n">
         <v>9</v>
@@ -12393,16 +12393,16 @@
         <v>1</v>
       </c>
       <c r="C342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D342" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E342" t="n">
         <v>9</v>
       </c>
       <c r="F342" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G342" t="n">
         <v>9</v>
@@ -12428,16 +12428,16 @@
         <v>1</v>
       </c>
       <c r="C343" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D343" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E343" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F343" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G343" t="n">
         <v>9</v>
@@ -12463,16 +12463,16 @@
         <v>1</v>
       </c>
       <c r="C344" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D344" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E344" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F344" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G344" t="n">
         <v>9</v>
@@ -12498,16 +12498,16 @@
         <v>1</v>
       </c>
       <c r="C345" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D345" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E345" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F345" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G345" t="n">
         <v>9</v>
@@ -12533,16 +12533,16 @@
         <v>1</v>
       </c>
       <c r="C346" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D346" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E346" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F346" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G346" t="n">
         <v>9</v>
@@ -12603,16 +12603,16 @@
         <v>1</v>
       </c>
       <c r="C348" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D348" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E348" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F348" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G348" t="n">
         <v>9</v>
@@ -12638,16 +12638,16 @@
         <v>1</v>
       </c>
       <c r="C349" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D349" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E349" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F349" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G349" t="n">
         <v>9</v>
@@ -12708,16 +12708,16 @@
         <v>1</v>
       </c>
       <c r="C351" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D351" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E351" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F351" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G351" t="n">
         <v>9</v>
@@ -12743,16 +12743,16 @@
         <v>1</v>
       </c>
       <c r="C352" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D352" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E352" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F352" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G352" t="n">
         <v>9</v>
@@ -12778,16 +12778,16 @@
         <v>1</v>
       </c>
       <c r="C353" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D353" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E353" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F353" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G353" t="n">
         <v>9</v>
@@ -12813,16 +12813,16 @@
         <v>1</v>
       </c>
       <c r="C354" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D354" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E354" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F354" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G354" t="n">
         <v>9</v>
@@ -12848,16 +12848,16 @@
         <v>1</v>
       </c>
       <c r="C355" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D355" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E355" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F355" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G355" t="n">
         <v>9</v>
@@ -12866,7 +12866,7 @@
         <v>8</v>
       </c>
       <c r="I355" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J355" t="n">
         <v>0</v>
@@ -12883,16 +12883,16 @@
         <v>1</v>
       </c>
       <c r="C356" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D356" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E356" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F356" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G356" t="n">
         <v>9</v>
@@ -12901,7 +12901,7 @@
         <v>8</v>
       </c>
       <c r="I356" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J356" t="n">
         <v>0</v>
@@ -12924,19 +12924,19 @@
         <v>42</v>
       </c>
       <c r="E357" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F357" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G357" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H357" t="n">
         <v>8</v>
       </c>
       <c r="I357" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J357" t="n">
         <v>0</v>
@@ -12953,19 +12953,19 @@
         <v>1</v>
       </c>
       <c r="C358" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D358" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E358" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F358" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G358" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H358" t="n">
         <v>8</v>
@@ -12988,19 +12988,19 @@
         <v>1</v>
       </c>
       <c r="C359" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D359" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E359" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F359" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G359" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H359" t="n">
         <v>8</v>
@@ -13023,19 +13023,19 @@
         <v>1</v>
       </c>
       <c r="C360" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D360" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E360" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F360" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G360" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H360" t="n">
         <v>8</v>
@@ -13058,19 +13058,19 @@
         <v>1</v>
       </c>
       <c r="C361" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D361" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E361" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F361" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G361" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H361" t="n">
         <v>8</v>
@@ -13093,19 +13093,19 @@
         <v>1</v>
       </c>
       <c r="C362" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D362" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E362" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F362" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G362" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H362" t="n">
         <v>8</v>
@@ -13128,19 +13128,19 @@
         <v>1</v>
       </c>
       <c r="C363" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D363" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E363" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F363" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G363" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H363" t="n">
         <v>8</v>
@@ -13163,19 +13163,19 @@
         <v>1</v>
       </c>
       <c r="C364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D364" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E364" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F364" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G364" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H364" t="n">
         <v>8</v>
@@ -13198,19 +13198,19 @@
         <v>1</v>
       </c>
       <c r="C365" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D365" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E365" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F365" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G365" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H365" t="n">
         <v>8</v>
@@ -13233,19 +13233,19 @@
         <v>1</v>
       </c>
       <c r="C366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D366" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E366" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F366" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G366" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H366" t="n">
         <v>8</v>
@@ -13303,19 +13303,19 @@
         <v>1</v>
       </c>
       <c r="C368" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D368" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E368" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F368" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G368" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H368" t="n">
         <v>8</v>
@@ -13338,19 +13338,19 @@
         <v>1</v>
       </c>
       <c r="C369" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D369" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E369" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F369" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G369" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H369" t="n">
         <v>8</v>
@@ -13373,19 +13373,19 @@
         <v>1</v>
       </c>
       <c r="C370" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D370" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E370" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F370" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G370" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H370" t="n">
         <v>8</v>
@@ -13408,19 +13408,19 @@
         <v>1</v>
       </c>
       <c r="C371" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D371" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E371" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F371" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G371" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H371" t="n">
         <v>8</v>
@@ -13443,19 +13443,19 @@
         <v>1</v>
       </c>
       <c r="C372" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D372" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E372" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F372" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G372" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H372" t="n">
         <v>8</v>
@@ -13478,13 +13478,13 @@
         <v>1</v>
       </c>
       <c r="C373" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D373" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E373" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F373" t="n">
         <v>9</v>
@@ -13513,13 +13513,13 @@
         <v>1</v>
       </c>
       <c r="C374" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D374" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E374" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F374" t="n">
         <v>9</v>
@@ -13548,13 +13548,13 @@
         <v>1</v>
       </c>
       <c r="C375" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D375" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E375" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F375" t="n">
         <v>9</v>
@@ -13583,13 +13583,13 @@
         <v>1</v>
       </c>
       <c r="C376" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D376" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E376" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F376" t="n">
         <v>9</v>
@@ -13618,13 +13618,13 @@
         <v>1</v>
       </c>
       <c r="C377" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D377" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E377" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F377" t="n">
         <v>9</v>
@@ -13688,13 +13688,13 @@
         <v>1</v>
       </c>
       <c r="C379" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D379" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E379" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F379" t="n">
         <v>9</v>
@@ -13723,13 +13723,13 @@
         <v>1</v>
       </c>
       <c r="C380" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D380" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E380" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F380" t="n">
         <v>9</v>
@@ -13758,13 +13758,13 @@
         <v>1</v>
       </c>
       <c r="C381" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D381" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E381" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F381" t="n">
         <v>9</v>
@@ -13793,13 +13793,13 @@
         <v>1</v>
       </c>
       <c r="C382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D382" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E382" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F382" t="n">
         <v>9</v>
@@ -13828,13 +13828,13 @@
         <v>1</v>
       </c>
       <c r="C383" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D383" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E383" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F383" t="n">
         <v>9</v>
@@ -13863,13 +13863,13 @@
         <v>1</v>
       </c>
       <c r="C384" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D384" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E384" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F384" t="n">
         <v>9</v>
@@ -13898,13 +13898,13 @@
         <v>1</v>
       </c>
       <c r="C385" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D385" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E385" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F385" t="n">
         <v>9</v>
@@ -13933,13 +13933,13 @@
         <v>1</v>
       </c>
       <c r="C386" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D386" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E386" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F386" t="n">
         <v>9</v>
@@ -13968,13 +13968,13 @@
         <v>1</v>
       </c>
       <c r="C387" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D387" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E387" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F387" t="n">
         <v>9</v>
@@ -14003,13 +14003,13 @@
         <v>1</v>
       </c>
       <c r="C388" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D388" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E388" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F388" t="n">
         <v>9</v>
@@ -14038,16 +14038,16 @@
         <v>1</v>
       </c>
       <c r="C389" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D389" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E389" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F389" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G389" t="n">
         <v>8</v>
@@ -14108,13 +14108,13 @@
         <v>1</v>
       </c>
       <c r="C391" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D391" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E391" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F391" t="n">
         <v>8</v>
@@ -14143,13 +14143,13 @@
         <v>1</v>
       </c>
       <c r="C392" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D392" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E392" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F392" t="n">
         <v>8</v>
@@ -14178,13 +14178,13 @@
         <v>1</v>
       </c>
       <c r="C393" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D393" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E393" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F393" t="n">
         <v>8</v>
@@ -14213,13 +14213,13 @@
         <v>1</v>
       </c>
       <c r="C394" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D394" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E394" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F394" t="n">
         <v>8</v>
@@ -14248,13 +14248,13 @@
         <v>1</v>
       </c>
       <c r="C395" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D395" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E395" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F395" t="n">
         <v>8</v>
@@ -14318,13 +14318,13 @@
         <v>1</v>
       </c>
       <c r="C397" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D397" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E397" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F397" t="n">
         <v>8</v>
@@ -14353,13 +14353,13 @@
         <v>1</v>
       </c>
       <c r="C398" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D398" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E398" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F398" t="n">
         <v>8</v>
@@ -14394,7 +14394,7 @@
         <v>41</v>
       </c>
       <c r="E399" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F399" t="n">
         <v>8</v>
@@ -14403,7 +14403,7 @@
         <v>8</v>
       </c>
       <c r="H399" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I399" t="n">
         <v>8</v>
@@ -14429,7 +14429,7 @@
         <v>41</v>
       </c>
       <c r="E400" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F400" t="n">
         <v>8</v>
@@ -14438,7 +14438,7 @@
         <v>8</v>
       </c>
       <c r="H400" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I400" t="n">
         <v>8</v>
@@ -14464,7 +14464,7 @@
         <v>41</v>
       </c>
       <c r="E401" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F401" t="n">
         <v>8</v>
@@ -14473,7 +14473,7 @@
         <v>8</v>
       </c>
       <c r="H401" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I401" t="n">
         <v>8</v>
@@ -14499,7 +14499,7 @@
         <v>41</v>
       </c>
       <c r="E402" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F402" t="n">
         <v>8</v>
@@ -14508,7 +14508,7 @@
         <v>8</v>
       </c>
       <c r="H402" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I402" t="n">
         <v>8</v>
@@ -14528,10 +14528,10 @@
         <v>1</v>
       </c>
       <c r="C403" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D403" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E403" t="n">
         <v>9</v>
@@ -14543,7 +14543,7 @@
         <v>8</v>
       </c>
       <c r="H403" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I403" t="n">
         <v>8</v>
@@ -14563,10 +14563,10 @@
         <v>1</v>
       </c>
       <c r="C404" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D404" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E404" t="n">
         <v>9</v>
@@ -14578,7 +14578,7 @@
         <v>8</v>
       </c>
       <c r="H404" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I404" t="n">
         <v>8</v>
@@ -14598,10 +14598,10 @@
         <v>1</v>
       </c>
       <c r="C405" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D405" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E405" t="n">
         <v>9</v>
@@ -14613,7 +14613,7 @@
         <v>8</v>
       </c>
       <c r="H405" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I405" t="n">
         <v>8</v>
@@ -14633,22 +14633,22 @@
         <v>1</v>
       </c>
       <c r="C406" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D406" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E406" t="n">
         <v>9</v>
       </c>
       <c r="F406" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G406" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H406" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I406" t="n">
         <v>8</v>
@@ -14668,22 +14668,22 @@
         <v>1</v>
       </c>
       <c r="C407" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D407" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E407" t="n">
         <v>9</v>
       </c>
       <c r="F407" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G407" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H407" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I407" t="n">
         <v>8</v>
@@ -14703,22 +14703,22 @@
         <v>1</v>
       </c>
       <c r="C408" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D408" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E408" t="n">
         <v>9</v>
       </c>
       <c r="F408" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G408" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H408" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I408" t="n">
         <v>8</v>
@@ -14773,22 +14773,22 @@
         <v>1</v>
       </c>
       <c r="C410" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D410" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E410" t="n">
         <v>9</v>
       </c>
       <c r="F410" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G410" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H410" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I410" t="n">
         <v>8</v>
@@ -14808,22 +14808,22 @@
         <v>1</v>
       </c>
       <c r="C411" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D411" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E411" t="n">
         <v>9</v>
       </c>
       <c r="F411" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G411" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H411" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I411" t="n">
         <v>8</v>
@@ -14843,22 +14843,22 @@
         <v>1</v>
       </c>
       <c r="C412" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D412" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E412" t="n">
         <v>9</v>
       </c>
       <c r="F412" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G412" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H412" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I412" t="n">
         <v>8</v>
@@ -14878,22 +14878,22 @@
         <v>1</v>
       </c>
       <c r="C413" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D413" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E413" t="n">
         <v>9</v>
       </c>
       <c r="F413" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G413" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H413" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I413" t="n">
         <v>8</v>
@@ -14913,22 +14913,22 @@
         <v>1</v>
       </c>
       <c r="C414" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D414" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E414" t="n">
         <v>9</v>
       </c>
       <c r="F414" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G414" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H414" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I414" t="n">
         <v>8</v>
@@ -14948,25 +14948,25 @@
         <v>1</v>
       </c>
       <c r="C415" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D415" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E415" t="n">
         <v>9</v>
       </c>
       <c r="F415" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G415" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H415" t="n">
         <v>8</v>
       </c>
       <c r="I415" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J415" t="n">
         <v>0</v>
@@ -14983,25 +14983,25 @@
         <v>1</v>
       </c>
       <c r="C416" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D416" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E416" t="n">
         <v>9</v>
       </c>
       <c r="F416" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G416" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H416" t="n">
         <v>8</v>
       </c>
       <c r="I416" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J416" t="n">
         <v>0</v>
@@ -15053,25 +15053,25 @@
         <v>1</v>
       </c>
       <c r="C418" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D418" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E418" t="n">
         <v>9</v>
       </c>
       <c r="F418" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G418" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H418" t="n">
         <v>8</v>
       </c>
       <c r="I418" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J418" t="n">
         <v>0</v>
@@ -15088,25 +15088,25 @@
         <v>1</v>
       </c>
       <c r="C419" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D419" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E419" t="n">
         <v>9</v>
       </c>
       <c r="F419" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G419" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H419" t="n">
         <v>8</v>
       </c>
       <c r="I419" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J419" t="n">
         <v>0</v>
@@ -15158,25 +15158,25 @@
         <v>1</v>
       </c>
       <c r="C421" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D421" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E421" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F421" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G421" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H421" t="n">
         <v>8</v>
       </c>
       <c r="I421" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J421" t="n">
         <v>0</v>
@@ -15193,25 +15193,25 @@
         <v>1</v>
       </c>
       <c r="C422" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D422" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E422" t="n">
         <v>8</v>
       </c>
       <c r="F422" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G422" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H422" t="n">
         <v>8</v>
       </c>
       <c r="I422" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J422" t="n">
         <v>0</v>
@@ -15228,16 +15228,16 @@
         <v>1</v>
       </c>
       <c r="C423" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D423" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E423" t="n">
         <v>8</v>
       </c>
       <c r="F423" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G423" t="n">
         <v>8</v>
@@ -15246,7 +15246,7 @@
         <v>8</v>
       </c>
       <c r="I423" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J423" t="n">
         <v>0</v>
@@ -15298,16 +15298,16 @@
         <v>1</v>
       </c>
       <c r="C425" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D425" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E425" t="n">
         <v>8</v>
       </c>
       <c r="F425" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G425" t="n">
         <v>8</v>
@@ -15316,7 +15316,7 @@
         <v>8</v>
       </c>
       <c r="I425" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J425" t="n">
         <v>0</v>
@@ -15333,16 +15333,16 @@
         <v>1</v>
       </c>
       <c r="C426" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D426" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E426" t="n">
         <v>8</v>
       </c>
       <c r="F426" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G426" t="n">
         <v>8</v>
@@ -15351,7 +15351,7 @@
         <v>8</v>
       </c>
       <c r="I426" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J426" t="n">
         <v>0</v>
@@ -15368,16 +15368,16 @@
         <v>1</v>
       </c>
       <c r="C427" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D427" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E427" t="n">
         <v>8</v>
       </c>
       <c r="F427" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G427" t="n">
         <v>8</v>
@@ -15386,7 +15386,7 @@
         <v>8</v>
       </c>
       <c r="I427" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J427" t="n">
         <v>0</v>
@@ -15403,16 +15403,16 @@
         <v>1</v>
       </c>
       <c r="C428" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D428" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E428" t="n">
         <v>8</v>
       </c>
       <c r="F428" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G428" t="n">
         <v>8</v>
@@ -15421,7 +15421,7 @@
         <v>8</v>
       </c>
       <c r="I428" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J428" t="n">
         <v>0</v>
@@ -15438,16 +15438,16 @@
         <v>1</v>
       </c>
       <c r="C429" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D429" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E429" t="n">
         <v>8</v>
       </c>
       <c r="F429" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G429" t="n">
         <v>8</v>
@@ -15456,7 +15456,7 @@
         <v>8</v>
       </c>
       <c r="I429" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J429" t="n">
         <v>0</v>
@@ -15473,16 +15473,16 @@
         <v>1</v>
       </c>
       <c r="C430" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D430" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E430" t="n">
         <v>8</v>
       </c>
       <c r="F430" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G430" t="n">
         <v>8</v>
@@ -15491,7 +15491,7 @@
         <v>8</v>
       </c>
       <c r="I430" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J430" t="n">
         <v>0</v>
@@ -15543,16 +15543,16 @@
         <v>1</v>
       </c>
       <c r="C432" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D432" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E432" t="n">
         <v>8</v>
       </c>
       <c r="F432" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G432" t="n">
         <v>8</v>
@@ -15561,7 +15561,7 @@
         <v>8</v>
       </c>
       <c r="I432" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J432" t="n">
         <v>0</v>
@@ -15578,16 +15578,16 @@
         <v>1</v>
       </c>
       <c r="C433" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D433" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E433" t="n">
         <v>8</v>
       </c>
       <c r="F433" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G433" t="n">
         <v>8</v>
@@ -15596,7 +15596,7 @@
         <v>8</v>
       </c>
       <c r="I433" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J433" t="n">
         <v>0</v>
@@ -15613,25 +15613,25 @@
         <v>1</v>
       </c>
       <c r="C434" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D434" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E434" t="n">
         <v>8</v>
       </c>
       <c r="F434" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G434" t="n">
         <v>8</v>
       </c>
       <c r="H434" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I434" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J434" t="n">
         <v>0</v>
@@ -15648,25 +15648,25 @@
         <v>1</v>
       </c>
       <c r="C435" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D435" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E435" t="n">
         <v>8</v>
       </c>
       <c r="F435" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G435" t="n">
         <v>8</v>
       </c>
       <c r="H435" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I435" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J435" t="n">
         <v>0</v>
@@ -15683,25 +15683,25 @@
         <v>1</v>
       </c>
       <c r="C436" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D436" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E436" t="n">
         <v>8</v>
       </c>
       <c r="F436" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G436" t="n">
         <v>8</v>
       </c>
       <c r="H436" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I436" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J436" t="n">
         <v>0</v>
@@ -15718,25 +15718,25 @@
         <v>1</v>
       </c>
       <c r="C437" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D437" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E437" t="n">
         <v>8</v>
       </c>
       <c r="F437" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G437" t="n">
         <v>8</v>
       </c>
       <c r="H437" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I437" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J437" t="n">
         <v>0</v>
@@ -15753,25 +15753,25 @@
         <v>1</v>
       </c>
       <c r="C438" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D438" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E438" t="n">
         <v>8</v>
       </c>
       <c r="F438" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G438" t="n">
         <v>8</v>
       </c>
       <c r="H438" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I438" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J438" t="n">
         <v>0</v>
@@ -15788,25 +15788,25 @@
         <v>1</v>
       </c>
       <c r="C439" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D439" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E439" t="n">
         <v>8</v>
       </c>
       <c r="F439" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G439" t="n">
         <v>8</v>
       </c>
       <c r="H439" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I439" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J439" t="n">
         <v>0</v>
@@ -15823,22 +15823,22 @@
         <v>1</v>
       </c>
       <c r="C440" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D440" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E440" t="n">
         <v>8</v>
       </c>
       <c r="F440" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G440" t="n">
         <v>8</v>
       </c>
       <c r="H440" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I440" t="n">
         <v>8</v>
@@ -15858,10 +15858,10 @@
         <v>1</v>
       </c>
       <c r="C441" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D441" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E441" t="n">
         <v>8</v>
@@ -15873,7 +15873,7 @@
         <v>8</v>
       </c>
       <c r="H441" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I441" t="n">
         <v>8</v>
@@ -15893,10 +15893,10 @@
         <v>1</v>
       </c>
       <c r="C442" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D442" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E442" t="n">
         <v>8</v>
@@ -15908,7 +15908,7 @@
         <v>8</v>
       </c>
       <c r="H442" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I442" t="n">
         <v>8</v>
@@ -15928,10 +15928,10 @@
         <v>1</v>
       </c>
       <c r="C443" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D443" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E443" t="n">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>8</v>
       </c>
       <c r="H443" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I443" t="n">
         <v>8</v>
@@ -15963,10 +15963,10 @@
         <v>1</v>
       </c>
       <c r="C444" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D444" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E444" t="n">
         <v>8</v>
@@ -15978,7 +15978,7 @@
         <v>8</v>
       </c>
       <c r="H444" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I444" t="n">
         <v>8</v>
@@ -16033,10 +16033,10 @@
         <v>1</v>
       </c>
       <c r="C446" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D446" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E446" t="n">
         <v>8</v>
@@ -16048,7 +16048,7 @@
         <v>8</v>
       </c>
       <c r="H446" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I446" t="n">
         <v>8</v>
@@ -16068,10 +16068,10 @@
         <v>1</v>
       </c>
       <c r="C447" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D447" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E447" t="n">
         <v>8</v>
@@ -16083,7 +16083,7 @@
         <v>8</v>
       </c>
       <c r="H447" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I447" t="n">
         <v>8</v>
@@ -16103,10 +16103,10 @@
         <v>1</v>
       </c>
       <c r="C448" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D448" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E448" t="n">
         <v>8</v>
@@ -16118,7 +16118,7 @@
         <v>8</v>
       </c>
       <c r="H448" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I448" t="n">
         <v>8</v>
@@ -16138,10 +16138,10 @@
         <v>1</v>
       </c>
       <c r="C449" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D449" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E449" t="n">
         <v>8</v>
@@ -16153,7 +16153,7 @@
         <v>8</v>
       </c>
       <c r="H449" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I449" t="n">
         <v>8</v>
@@ -17188,16 +17188,16 @@
         <v>1</v>
       </c>
       <c r="C479" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D479" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E479" t="n">
         <v>8</v>
       </c>
       <c r="F479" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G479" t="n">
         <v>8</v>
@@ -17223,16 +17223,16 @@
         <v>1</v>
       </c>
       <c r="C480" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D480" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E480" t="n">
         <v>8</v>
       </c>
       <c r="F480" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G480" t="n">
         <v>8</v>
@@ -17258,16 +17258,16 @@
         <v>1</v>
       </c>
       <c r="C481" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D481" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E481" t="n">
         <v>8</v>
       </c>
       <c r="F481" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G481" t="n">
         <v>8</v>
@@ -17293,16 +17293,16 @@
         <v>1</v>
       </c>
       <c r="C482" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D482" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E482" t="n">
         <v>8</v>
       </c>
       <c r="F482" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G482" t="n">
         <v>8</v>
@@ -17328,16 +17328,16 @@
         <v>1</v>
       </c>
       <c r="C483" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D483" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E483" t="n">
         <v>8</v>
       </c>
       <c r="F483" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G483" t="n">
         <v>8</v>
@@ -17363,16 +17363,16 @@
         <v>1</v>
       </c>
       <c r="C484" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D484" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E484" t="n">
         <v>8</v>
       </c>
       <c r="F484" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G484" t="n">
         <v>8</v>
@@ -17398,16 +17398,16 @@
         <v>1</v>
       </c>
       <c r="C485" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D485" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E485" t="n">
         <v>8</v>
       </c>
       <c r="F485" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G485" t="n">
         <v>8</v>
@@ -17433,16 +17433,16 @@
         <v>1</v>
       </c>
       <c r="C486" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D486" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E486" t="n">
         <v>8</v>
       </c>
       <c r="F486" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G486" t="n">
         <v>8</v>
@@ -17468,16 +17468,16 @@
         <v>1</v>
       </c>
       <c r="C487" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D487" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E487" t="n">
         <v>8</v>
       </c>
       <c r="F487" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G487" t="n">
         <v>8</v>
@@ -17503,16 +17503,16 @@
         <v>1</v>
       </c>
       <c r="C488" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D488" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E488" t="n">
         <v>8</v>
       </c>
       <c r="F488" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G488" t="n">
         <v>8</v>
@@ -17538,16 +17538,16 @@
         <v>1</v>
       </c>
       <c r="C489" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D489" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E489" t="n">
         <v>8</v>
       </c>
       <c r="F489" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G489" t="n">
         <v>8</v>
@@ -17573,16 +17573,16 @@
         <v>1</v>
       </c>
       <c r="C490" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D490" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E490" t="n">
         <v>8</v>
       </c>
       <c r="F490" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G490" t="n">
         <v>8</v>
@@ -17608,16 +17608,16 @@
         <v>1</v>
       </c>
       <c r="C491" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D491" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E491" t="n">
         <v>8</v>
       </c>
       <c r="F491" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G491" t="n">
         <v>8</v>
@@ -17678,16 +17678,16 @@
         <v>1</v>
       </c>
       <c r="C493" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D493" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E493" t="n">
         <v>8</v>
       </c>
       <c r="F493" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G493" t="n">
         <v>8</v>
@@ -17713,16 +17713,16 @@
         <v>1</v>
       </c>
       <c r="C494" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D494" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E494" t="n">
         <v>8</v>
       </c>
       <c r="F494" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G494" t="n">
         <v>8</v>
@@ -17993,13 +17993,13 @@
         <v>1</v>
       </c>
       <c r="C502" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D502" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E502" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F502" t="n">
         <v>8</v>
@@ -18028,13 +18028,13 @@
         <v>1</v>
       </c>
       <c r="C503" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D503" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E503" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F503" t="n">
         <v>8</v>
@@ -18098,13 +18098,13 @@
         <v>1</v>
       </c>
       <c r="C505" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D505" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E505" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F505" t="n">
         <v>8</v>
@@ -18133,13 +18133,13 @@
         <v>1</v>
       </c>
       <c r="C506" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D506" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E506" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F506" t="n">
         <v>8</v>
@@ -18168,13 +18168,13 @@
         <v>1</v>
       </c>
       <c r="C507" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D507" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E507" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F507" t="n">
         <v>8</v>
@@ -18203,13 +18203,13 @@
         <v>1</v>
       </c>
       <c r="C508" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D508" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E508" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F508" t="n">
         <v>8</v>
@@ -18238,13 +18238,13 @@
         <v>1</v>
       </c>
       <c r="C509" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D509" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E509" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F509" t="n">
         <v>8</v>
@@ -18273,13 +18273,13 @@
         <v>1</v>
       </c>
       <c r="C510" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D510" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E510" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F510" t="n">
         <v>8</v>
@@ -18308,13 +18308,13 @@
         <v>1</v>
       </c>
       <c r="C511" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D511" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E511" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F511" t="n">
         <v>8</v>
@@ -18343,13 +18343,13 @@
         <v>1</v>
       </c>
       <c r="C512" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D512" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E512" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F512" t="n">
         <v>8</v>
@@ -18378,13 +18378,13 @@
         <v>1</v>
       </c>
       <c r="C513" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D513" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E513" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F513" t="n">
         <v>8</v>
@@ -18396,7 +18396,7 @@
         <v>8</v>
       </c>
       <c r="I513" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J513" t="n">
         <v>0</v>
@@ -18448,13 +18448,13 @@
         <v>1</v>
       </c>
       <c r="C515" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D515" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E515" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F515" t="n">
         <v>8</v>
@@ -18466,7 +18466,7 @@
         <v>8</v>
       </c>
       <c r="I515" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J515" t="n">
         <v>0</v>
@@ -18483,13 +18483,13 @@
         <v>1</v>
       </c>
       <c r="C516" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D516" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E516" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F516" t="n">
         <v>8</v>
@@ -18501,7 +18501,7 @@
         <v>8</v>
       </c>
       <c r="I516" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J516" t="n">
         <v>0</v>
@@ -18518,13 +18518,13 @@
         <v>1</v>
       </c>
       <c r="C517" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D517" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E517" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F517" t="n">
         <v>8</v>
@@ -18536,7 +18536,7 @@
         <v>8</v>
       </c>
       <c r="I517" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J517" t="n">
         <v>0</v>
@@ -18553,13 +18553,13 @@
         <v>1</v>
       </c>
       <c r="C518" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D518" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E518" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F518" t="n">
         <v>8</v>
@@ -18571,7 +18571,7 @@
         <v>8</v>
       </c>
       <c r="I518" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J518" t="n">
         <v>0</v>
@@ -18588,10 +18588,10 @@
         <v>1</v>
       </c>
       <c r="C519" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D519" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E519" t="n">
         <v>8</v>
@@ -18606,7 +18606,7 @@
         <v>8</v>
       </c>
       <c r="I519" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J519" t="n">
         <v>0</v>
@@ -18623,10 +18623,10 @@
         <v>1</v>
       </c>
       <c r="C520" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D520" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E520" t="n">
         <v>8</v>
@@ -18641,7 +18641,7 @@
         <v>8</v>
       </c>
       <c r="I520" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J520" t="n">
         <v>0</v>
@@ -18693,10 +18693,10 @@
         <v>1</v>
       </c>
       <c r="C522" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D522" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E522" t="n">
         <v>8</v>
@@ -18711,7 +18711,7 @@
         <v>8</v>
       </c>
       <c r="I522" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J522" t="n">
         <v>0</v>
@@ -18728,10 +18728,10 @@
         <v>1</v>
       </c>
       <c r="C523" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D523" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E523" t="n">
         <v>8</v>
@@ -18740,16 +18740,16 @@
         <v>8</v>
       </c>
       <c r="G523" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H523" t="n">
         <v>8</v>
       </c>
       <c r="I523" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J523" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K523" t="n">
         <v>0</v>
@@ -18763,10 +18763,10 @@
         <v>1</v>
       </c>
       <c r="C524" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D524" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E524" t="n">
         <v>8</v>
@@ -18775,16 +18775,16 @@
         <v>8</v>
       </c>
       <c r="G524" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H524" t="n">
         <v>8</v>
       </c>
       <c r="I524" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J524" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K524" t="n">
         <v>0</v>
@@ -18833,10 +18833,10 @@
         <v>1</v>
       </c>
       <c r="C526" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D526" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E526" t="n">
         <v>8</v>
@@ -18845,16 +18845,16 @@
         <v>8</v>
       </c>
       <c r="G526" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H526" t="n">
         <v>8</v>
       </c>
       <c r="I526" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J526" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K526" t="n">
         <v>0</v>
@@ -18868,10 +18868,10 @@
         <v>1</v>
       </c>
       <c r="C527" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D527" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E527" t="n">
         <v>8</v>
@@ -18880,16 +18880,16 @@
         <v>8</v>
       </c>
       <c r="G527" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H527" t="n">
         <v>8</v>
       </c>
       <c r="I527" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J527" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K527" t="n">
         <v>0</v>
@@ -18903,10 +18903,10 @@
         <v>1</v>
       </c>
       <c r="C528" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D528" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E528" t="n">
         <v>8</v>
@@ -18915,16 +18915,16 @@
         <v>8</v>
       </c>
       <c r="G528" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H528" t="n">
         <v>8</v>
       </c>
       <c r="I528" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J528" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K528" t="n">
         <v>0</v>
@@ -18938,28 +18938,28 @@
         <v>1</v>
       </c>
       <c r="C529" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D529" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E529" t="n">
         <v>8</v>
       </c>
       <c r="F529" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G529" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H529" t="n">
         <v>8</v>
       </c>
       <c r="I529" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J529" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K529" t="n">
         <v>0</v>
@@ -18973,28 +18973,28 @@
         <v>1</v>
       </c>
       <c r="C530" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D530" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E530" t="n">
         <v>8</v>
       </c>
       <c r="F530" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G530" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H530" t="n">
         <v>8</v>
       </c>
       <c r="I530" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J530" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K530" t="n">
         <v>0</v>

--- a/Result/Agents.xlsx
+++ b/Result/Agents.xlsx
@@ -3970,13 +3970,13 @@
         <v>9</v>
       </c>
       <c r="G101" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H101" t="n">
         <v>9</v>
       </c>
       <c r="I101" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -4040,13 +4040,13 @@
         <v>9</v>
       </c>
       <c r="G103" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H103" t="n">
         <v>9</v>
       </c>
       <c r="I103" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -4075,13 +4075,13 @@
         <v>9</v>
       </c>
       <c r="G104" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H104" t="n">
         <v>9</v>
       </c>
       <c r="I104" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -4110,13 +4110,13 @@
         <v>9</v>
       </c>
       <c r="G105" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H105" t="n">
         <v>9</v>
       </c>
       <c r="I105" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -4180,13 +4180,13 @@
         <v>9</v>
       </c>
       <c r="G107" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H107" t="n">
         <v>9</v>
       </c>
       <c r="I107" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -4215,13 +4215,13 @@
         <v>9</v>
       </c>
       <c r="G108" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H108" t="n">
         <v>9</v>
       </c>
       <c r="I108" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -4250,13 +4250,13 @@
         <v>9</v>
       </c>
       <c r="G109" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H109" t="n">
         <v>9</v>
       </c>
       <c r="I109" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -4285,13 +4285,13 @@
         <v>9</v>
       </c>
       <c r="G110" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H110" t="n">
         <v>9</v>
       </c>
       <c r="I110" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -4320,13 +4320,13 @@
         <v>9</v>
       </c>
       <c r="G111" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H111" t="n">
         <v>9</v>
       </c>
       <c r="I111" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -4390,13 +4390,13 @@
         <v>9</v>
       </c>
       <c r="G113" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H113" t="n">
         <v>9</v>
       </c>
       <c r="I113" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -4425,13 +4425,13 @@
         <v>9</v>
       </c>
       <c r="G114" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H114" t="n">
         <v>9</v>
       </c>
       <c r="I114" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -4460,13 +4460,13 @@
         <v>9</v>
       </c>
       <c r="G115" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H115" t="n">
         <v>9</v>
       </c>
       <c r="I115" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -4495,13 +4495,13 @@
         <v>9</v>
       </c>
       <c r="G116" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H116" t="n">
         <v>9</v>
       </c>
       <c r="I116" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -4530,13 +4530,13 @@
         <v>9</v>
       </c>
       <c r="G117" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H117" t="n">
         <v>9</v>
       </c>
       <c r="I117" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -4565,13 +4565,13 @@
         <v>9</v>
       </c>
       <c r="G118" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H118" t="n">
         <v>9</v>
       </c>
       <c r="I118" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -4600,13 +4600,13 @@
         <v>9</v>
       </c>
       <c r="G119" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H119" t="n">
         <v>9</v>
       </c>
       <c r="I119" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -4635,13 +4635,13 @@
         <v>9</v>
       </c>
       <c r="G120" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H120" t="n">
         <v>9</v>
       </c>
       <c r="I120" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -4658,25 +4658,25 @@
         <v>1</v>
       </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E121" t="n">
         <v>9</v>
       </c>
       <c r="F121" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G121" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H121" t="n">
         <v>9</v>
       </c>
       <c r="I121" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -4693,25 +4693,25 @@
         <v>1</v>
       </c>
       <c r="C122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D122" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E122" t="n">
         <v>9</v>
       </c>
       <c r="F122" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G122" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H122" t="n">
         <v>9</v>
       </c>
       <c r="I122" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -4728,25 +4728,25 @@
         <v>1</v>
       </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D123" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E123" t="n">
         <v>9</v>
       </c>
       <c r="F123" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G123" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H123" t="n">
         <v>9</v>
       </c>
       <c r="I123" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -4798,25 +4798,25 @@
         <v>1</v>
       </c>
       <c r="C125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E125" t="n">
         <v>9</v>
       </c>
       <c r="F125" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G125" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H125" t="n">
         <v>9</v>
       </c>
       <c r="I125" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -4833,25 +4833,25 @@
         <v>1</v>
       </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D126" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E126" t="n">
         <v>9</v>
       </c>
       <c r="F126" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G126" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H126" t="n">
         <v>9</v>
       </c>
       <c r="I126" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -4868,25 +4868,25 @@
         <v>1</v>
       </c>
       <c r="C127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D127" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E127" t="n">
         <v>9</v>
       </c>
       <c r="F127" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G127" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H127" t="n">
         <v>9</v>
       </c>
       <c r="I127" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -4903,25 +4903,25 @@
         <v>1</v>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D128" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E128" t="n">
         <v>9</v>
       </c>
       <c r="F128" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G128" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H128" t="n">
         <v>9</v>
       </c>
       <c r="I128" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -4938,22 +4938,22 @@
         <v>1</v>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D129" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E129" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F129" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G129" t="n">
         <v>8</v>
       </c>
       <c r="H129" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I129" t="n">
         <v>9</v>
@@ -4973,22 +4973,22 @@
         <v>1</v>
       </c>
       <c r="C130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D130" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E130" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F130" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G130" t="n">
         <v>8</v>
       </c>
       <c r="H130" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I130" t="n">
         <v>9</v>
@@ -5008,22 +5008,22 @@
         <v>1</v>
       </c>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D131" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E131" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F131" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G131" t="n">
         <v>8</v>
       </c>
       <c r="H131" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I131" t="n">
         <v>9</v>
@@ -5043,22 +5043,22 @@
         <v>1</v>
       </c>
       <c r="C132" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D132" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E132" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F132" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G132" t="n">
         <v>8</v>
       </c>
       <c r="H132" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I132" t="n">
         <v>9</v>
@@ -5078,22 +5078,22 @@
         <v>1</v>
       </c>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D133" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E133" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F133" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G133" t="n">
         <v>8</v>
       </c>
       <c r="H133" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I133" t="n">
         <v>9</v>
@@ -5113,16 +5113,16 @@
         <v>1</v>
       </c>
       <c r="C134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D134" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E134" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F134" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G134" t="n">
         <v>8</v>
@@ -5148,16 +5148,16 @@
         <v>1</v>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D135" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E135" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F135" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G135" t="n">
         <v>8</v>
@@ -5183,13 +5183,13 @@
         <v>1</v>
       </c>
       <c r="C136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D136" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E136" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F136" t="n">
         <v>8</v>
@@ -5988,10 +5988,10 @@
         <v>1</v>
       </c>
       <c r="C159" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D159" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E159" t="n">
         <v>8</v>
@@ -6006,7 +6006,7 @@
         <v>8</v>
       </c>
       <c r="I159" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -6058,10 +6058,10 @@
         <v>1</v>
       </c>
       <c r="C161" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D161" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E161" t="n">
         <v>8</v>
@@ -6076,7 +6076,7 @@
         <v>8</v>
       </c>
       <c r="I161" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -6093,10 +6093,10 @@
         <v>1</v>
       </c>
       <c r="C162" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D162" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E162" t="n">
         <v>8</v>
@@ -6111,7 +6111,7 @@
         <v>8</v>
       </c>
       <c r="I162" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -6128,10 +6128,10 @@
         <v>1</v>
       </c>
       <c r="C163" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D163" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E163" t="n">
         <v>8</v>
@@ -6146,7 +6146,7 @@
         <v>8</v>
       </c>
       <c r="I163" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -6163,10 +6163,10 @@
         <v>1</v>
       </c>
       <c r="C164" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D164" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E164" t="n">
         <v>8</v>
@@ -6181,7 +6181,7 @@
         <v>8</v>
       </c>
       <c r="I164" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -6198,10 +6198,10 @@
         <v>1</v>
       </c>
       <c r="C165" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D165" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E165" t="n">
         <v>8</v>
@@ -6216,7 +6216,7 @@
         <v>8</v>
       </c>
       <c r="I165" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -6233,10 +6233,10 @@
         <v>1</v>
       </c>
       <c r="C166" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D166" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E166" t="n">
         <v>8</v>
@@ -6251,7 +6251,7 @@
         <v>8</v>
       </c>
       <c r="I166" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -6268,10 +6268,10 @@
         <v>1</v>
       </c>
       <c r="C167" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D167" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E167" t="n">
         <v>8</v>
@@ -6286,7 +6286,7 @@
         <v>8</v>
       </c>
       <c r="I167" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -6303,10 +6303,10 @@
         <v>1</v>
       </c>
       <c r="C168" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D168" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E168" t="n">
         <v>8</v>
@@ -6321,7 +6321,7 @@
         <v>8</v>
       </c>
       <c r="I168" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -6338,10 +6338,10 @@
         <v>1</v>
       </c>
       <c r="C169" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D169" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E169" t="n">
         <v>8</v>
@@ -6356,7 +6356,7 @@
         <v>8</v>
       </c>
       <c r="I169" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -6408,10 +6408,10 @@
         <v>1</v>
       </c>
       <c r="C171" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D171" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E171" t="n">
         <v>8</v>
@@ -6426,7 +6426,7 @@
         <v>8</v>
       </c>
       <c r="I171" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -6478,10 +6478,10 @@
         <v>1</v>
       </c>
       <c r="C173" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D173" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E173" t="n">
         <v>8</v>
@@ -6496,7 +6496,7 @@
         <v>8</v>
       </c>
       <c r="I173" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>1</v>
       </c>
       <c r="C174" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D174" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E174" t="n">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>8</v>
       </c>
       <c r="I174" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -6548,10 +6548,10 @@
         <v>1</v>
       </c>
       <c r="C175" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D175" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E175" t="n">
         <v>8</v>
@@ -6566,7 +6566,7 @@
         <v>8</v>
       </c>
       <c r="I175" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -6583,10 +6583,10 @@
         <v>1</v>
       </c>
       <c r="C176" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D176" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E176" t="n">
         <v>8</v>
@@ -6601,7 +6601,7 @@
         <v>8</v>
       </c>
       <c r="I176" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -6618,10 +6618,10 @@
         <v>1</v>
       </c>
       <c r="C177" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D177" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E177" t="n">
         <v>8</v>
@@ -6636,7 +6636,7 @@
         <v>8</v>
       </c>
       <c r="I177" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -6653,10 +6653,10 @@
         <v>1</v>
       </c>
       <c r="C178" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D178" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E178" t="n">
         <v>8</v>
@@ -6671,7 +6671,7 @@
         <v>8</v>
       </c>
       <c r="I178" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -6688,10 +6688,10 @@
         <v>1</v>
       </c>
       <c r="C179" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D179" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E179" t="n">
         <v>8</v>
@@ -6706,7 +6706,7 @@
         <v>8</v>
       </c>
       <c r="I179" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -6723,10 +6723,10 @@
         <v>1</v>
       </c>
       <c r="C180" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D180" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E180" t="n">
         <v>8</v>
@@ -6741,7 +6741,7 @@
         <v>8</v>
       </c>
       <c r="I180" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -6758,10 +6758,10 @@
         <v>1</v>
       </c>
       <c r="C181" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D181" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E181" t="n">
         <v>8</v>
@@ -6776,7 +6776,7 @@
         <v>8</v>
       </c>
       <c r="I181" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -6793,10 +6793,10 @@
         <v>1</v>
       </c>
       <c r="C182" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D182" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E182" t="n">
         <v>8</v>
@@ -6811,7 +6811,7 @@
         <v>8</v>
       </c>
       <c r="I182" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -6828,10 +6828,10 @@
         <v>1</v>
       </c>
       <c r="C183" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D183" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E183" t="n">
         <v>8</v>
@@ -6846,7 +6846,7 @@
         <v>8</v>
       </c>
       <c r="I183" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -6898,10 +6898,10 @@
         <v>1</v>
       </c>
       <c r="C185" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D185" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E185" t="n">
         <v>8</v>
@@ -6916,7 +6916,7 @@
         <v>8</v>
       </c>
       <c r="I185" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -6933,10 +6933,10 @@
         <v>1</v>
       </c>
       <c r="C186" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D186" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E186" t="n">
         <v>8</v>
@@ -6951,7 +6951,7 @@
         <v>8</v>
       </c>
       <c r="I186" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -6968,10 +6968,10 @@
         <v>1</v>
       </c>
       <c r="C187" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D187" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E187" t="n">
         <v>8</v>
@@ -6986,7 +6986,7 @@
         <v>8</v>
       </c>
       <c r="I187" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -7038,10 +7038,10 @@
         <v>1</v>
       </c>
       <c r="C189" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D189" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E189" t="n">
         <v>8</v>
@@ -7056,7 +7056,7 @@
         <v>8</v>
       </c>
       <c r="I189" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -7073,10 +7073,10 @@
         <v>1</v>
       </c>
       <c r="C190" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D190" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E190" t="n">
         <v>8</v>
@@ -7091,7 +7091,7 @@
         <v>8</v>
       </c>
       <c r="I190" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -7108,10 +7108,10 @@
         <v>1</v>
       </c>
       <c r="C191" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D191" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E191" t="n">
         <v>8</v>
@@ -7126,7 +7126,7 @@
         <v>8</v>
       </c>
       <c r="I191" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -7143,10 +7143,10 @@
         <v>1</v>
       </c>
       <c r="C192" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D192" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E192" t="n">
         <v>8</v>
@@ -7161,7 +7161,7 @@
         <v>8</v>
       </c>
       <c r="I192" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -7178,10 +7178,10 @@
         <v>1</v>
       </c>
       <c r="C193" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D193" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E193" t="n">
         <v>8</v>
@@ -7196,7 +7196,7 @@
         <v>8</v>
       </c>
       <c r="I193" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -7213,10 +7213,10 @@
         <v>1</v>
       </c>
       <c r="C194" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D194" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E194" t="n">
         <v>8</v>
@@ -7231,7 +7231,7 @@
         <v>8</v>
       </c>
       <c r="I194" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -8088,10 +8088,10 @@
         <v>1</v>
       </c>
       <c r="C219" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D219" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E219" t="n">
         <v>8</v>
@@ -8100,7 +8100,7 @@
         <v>8</v>
       </c>
       <c r="G219" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H219" t="n">
         <v>8</v>
@@ -8123,10 +8123,10 @@
         <v>1</v>
       </c>
       <c r="C220" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D220" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E220" t="n">
         <v>8</v>
@@ -8135,7 +8135,7 @@
         <v>8</v>
       </c>
       <c r="G220" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H220" t="n">
         <v>8</v>
@@ -8158,10 +8158,10 @@
         <v>1</v>
       </c>
       <c r="C221" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D221" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E221" t="n">
         <v>8</v>
@@ -8170,7 +8170,7 @@
         <v>8</v>
       </c>
       <c r="G221" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H221" t="n">
         <v>8</v>
@@ -8193,10 +8193,10 @@
         <v>1</v>
       </c>
       <c r="C222" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D222" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E222" t="n">
         <v>8</v>
@@ -8205,7 +8205,7 @@
         <v>8</v>
       </c>
       <c r="G222" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H222" t="n">
         <v>8</v>
@@ -12463,10 +12463,10 @@
         <v>1</v>
       </c>
       <c r="C344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D344" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E344" t="n">
         <v>9</v>
@@ -12481,7 +12481,7 @@
         <v>8</v>
       </c>
       <c r="I344" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J344" t="n">
         <v>0</v>
@@ -12498,10 +12498,10 @@
         <v>1</v>
       </c>
       <c r="C345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D345" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E345" t="n">
         <v>9</v>
@@ -12516,7 +12516,7 @@
         <v>8</v>
       </c>
       <c r="I345" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J345" t="n">
         <v>0</v>
@@ -12533,10 +12533,10 @@
         <v>1</v>
       </c>
       <c r="C346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D346" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E346" t="n">
         <v>9</v>
@@ -12551,7 +12551,7 @@
         <v>8</v>
       </c>
       <c r="I346" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J346" t="n">
         <v>0</v>
@@ -12603,10 +12603,10 @@
         <v>1</v>
       </c>
       <c r="C348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D348" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E348" t="n">
         <v>9</v>
@@ -12621,7 +12621,7 @@
         <v>8</v>
       </c>
       <c r="I348" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J348" t="n">
         <v>0</v>
@@ -12638,10 +12638,10 @@
         <v>1</v>
       </c>
       <c r="C349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D349" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E349" t="n">
         <v>9</v>
@@ -12656,7 +12656,7 @@
         <v>8</v>
       </c>
       <c r="I349" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J349" t="n">
         <v>0</v>
@@ -12708,10 +12708,10 @@
         <v>1</v>
       </c>
       <c r="C351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D351" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E351" t="n">
         <v>9</v>
@@ -12726,7 +12726,7 @@
         <v>8</v>
       </c>
       <c r="I351" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J351" t="n">
         <v>0</v>
@@ -12743,10 +12743,10 @@
         <v>1</v>
       </c>
       <c r="C352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D352" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E352" t="n">
         <v>9</v>
@@ -12761,7 +12761,7 @@
         <v>8</v>
       </c>
       <c r="I352" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J352" t="n">
         <v>0</v>
@@ -12778,10 +12778,10 @@
         <v>1</v>
       </c>
       <c r="C353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D353" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E353" t="n">
         <v>9</v>
@@ -12796,7 +12796,7 @@
         <v>8</v>
       </c>
       <c r="I353" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J353" t="n">
         <v>0</v>
@@ -12813,10 +12813,10 @@
         <v>1</v>
       </c>
       <c r="C354" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D354" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E354" t="n">
         <v>9</v>
@@ -12831,7 +12831,7 @@
         <v>8</v>
       </c>
       <c r="I354" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J354" t="n">
         <v>0</v>
@@ -12918,10 +12918,10 @@
         <v>1</v>
       </c>
       <c r="C357" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D357" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E357" t="n">
         <v>9</v>
@@ -12930,7 +12930,7 @@
         <v>9</v>
       </c>
       <c r="G357" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H357" t="n">
         <v>8</v>
@@ -12953,10 +12953,10 @@
         <v>1</v>
       </c>
       <c r="C358" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D358" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E358" t="n">
         <v>9</v>
@@ -12965,7 +12965,7 @@
         <v>9</v>
       </c>
       <c r="G358" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H358" t="n">
         <v>8</v>
@@ -12988,10 +12988,10 @@
         <v>1</v>
       </c>
       <c r="C359" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D359" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E359" t="n">
         <v>9</v>
@@ -13000,7 +13000,7 @@
         <v>9</v>
       </c>
       <c r="G359" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H359" t="n">
         <v>8</v>
@@ -13023,10 +13023,10 @@
         <v>1</v>
       </c>
       <c r="C360" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D360" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E360" t="n">
         <v>9</v>
@@ -13035,7 +13035,7 @@
         <v>9</v>
       </c>
       <c r="G360" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H360" t="n">
         <v>8</v>

--- a/Result/Agents.xlsx
+++ b/Result/Agents.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pruebas\Proyect_WFM\Result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBBBED1-DC16-42F7-9275-43F73F7041F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20637404-7422-4141-AEC8-B495B8CF9127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -133,8 +133,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1393,7 +1394,7 @@
       <c r="Q17">
         <v>0</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="1">
         <v>0</v>
       </c>
     </row>
